--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="369">
   <si>
     <r>
       <rPr>
@@ -1535,44 +1535,36 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">링 단자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배터리 단자 볼트 크기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) + 250 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">평형 단자 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">250 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">규격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6.3mm) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">절연 암 평형 단자 </t>
     </r>
     <r>
       <rPr>
@@ -1593,10 +1585,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">배터리·릴레이 소켓·퓨즈 홀더 연결</t>
-  </si>
-  <si>
-    <t xml:space="preserve">배터리 단자 볼트 지름 실측 후 링 단자 크기 결정</t>
+    <t xml:space="preserve">퓨즈 홀더·릴레이 소켓 연결 (배터리 쪽은 키트 선 단자 재사용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배터리 단자 = 6.3mm 평형 탭(사진 확인) · 홀더·소켓에 단자 포함이면 생략</t>
   </si>
   <si>
     <t xml:space="preserve">저항</t>
@@ -1710,6 +1702,40 @@
   </si>
   <si>
     <t xml:space="preserve">선택</t>
+  </si>
+  <si>
+    <t xml:space="preserve">디지털 캘리퍼스</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.01mm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 150mm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">쿠폰·핀 구멍·축 지름 확인</t>
   </si>
   <si>
     <t xml:space="preserve">배송비</t>
@@ -3247,7 +3273,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4892,7 +4918,7 @@
       <c r="B55" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="4" t="s">
         <v>197</v>
       </c>
       <c r="D55" s="4" t="n">
@@ -5016,53 +5042,84 @@
       <c r="B59" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="4" t="s">
         <v>214</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="7" t="n">
         <f aca="false">D59*F59</f>
         <v>0</v>
       </c>
-      <c r="H59" s="5"/>
+      <c r="H59" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="I59" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J59" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G60" s="10" t="n">
-        <f aca="false">SUMIFS(G5:G59,I5:I59,"확정")</f>
-        <v>198400</v>
+      <c r="D60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="G60" s="7" t="n">
+        <f aca="false">D60*F60</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G61" s="10" t="n">
-        <f aca="false">SUM(G5:G59)</f>
+        <f aca="false">SUMIFS(G5:G60,I5:I60,"확정")</f>
         <v>198400</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G62" s="11" t="n">
-        <f aca="false">COUNTBLANK(F5:F59)</f>
-        <v>38</v>
+        <v>221</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <f aca="false">SUM(G5:G60)</f>
+        <v>198400</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <f aca="false">COUNTBLANK(F5:F60)</f>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5097,12 +5154,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5142,10 +5199,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2</v>
@@ -5161,13 +5218,13 @@
         <v>12000</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5194,13 +5251,13 @@
         <v>3500</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5233,7 +5290,7 @@
         <v>16</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5260,13 +5317,13 @@
         <v>9200</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5293,13 +5350,13 @@
         <v>11300</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5332,7 +5389,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5365,7 +5422,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5392,13 +5449,13 @@
         <v>800</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5431,7 +5488,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5464,7 +5521,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5491,13 +5548,13 @@
         <v>9000</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5508,7 +5565,7 @@
         <v>135</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1</v>
@@ -5524,13 +5581,13 @@
         <v>8000</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5557,13 +5614,13 @@
         <v>4500</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5571,10 +5628,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1</v>
@@ -5590,13 +5647,13 @@
         <v>350</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5623,13 +5680,13 @@
         <v>9600</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5640,7 +5697,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>1</v>
@@ -5656,13 +5713,13 @@
         <v>16000</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5673,7 +5730,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>3</v>
@@ -5693,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5704,7 +5761,7 @@
         <v>60</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>3</v>
@@ -5726,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5737,7 +5794,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1</v>
@@ -5753,13 +5810,13 @@
         <v>8360</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5767,7 +5824,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>102</v>
@@ -5784,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>16</v>
@@ -5798,10 +5855,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>29</v>
@@ -5815,13 +5872,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5846,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>16</v>
@@ -5877,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>16</v>
@@ -5894,13 +5951,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7" t="n">
@@ -5908,13 +5965,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5922,16 +5979,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>22900</v>
@@ -5945,7 +6002,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5953,16 +6010,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="15" t="n">
@@ -5970,13 +6027,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5987,7 +6044,7 @@
         <v>56</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" s="13" t="n">
         <v>3</v>
@@ -6003,13 +6060,13 @@
         <v>25080</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6017,10 +6074,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D32" s="13" t="n">
         <v>1</v>
@@ -6034,10 +6091,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J32" s="14"/>
     </row>
@@ -6046,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>131</v>
@@ -6063,10 +6120,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J33" s="14"/>
     </row>
@@ -6075,10 +6132,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D34" s="13" t="n">
         <v>1</v>
@@ -6092,13 +6149,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6109,7 +6166,7 @@
         <v>182</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D35" s="13" t="n">
         <v>1</v>
@@ -6123,16 +6180,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G36" s="10" t="n">
         <f aca="false">SUMIFS(G5:G35,I5:I35,"확정")</f>
@@ -6141,7 +6198,7 @@
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G37" s="10" t="n">
         <f aca="false">SUM(G5:G35)</f>
@@ -6150,7 +6207,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G38" s="11" t="n">
         <f aca="false">COUNTBLANK(F5:F35)</f>
@@ -6189,12 +6246,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6237,7 +6294,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2</v>
@@ -6251,13 +6308,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6268,7 +6325,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
@@ -6288,7 +6345,7 @@
         <v>16</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6299,7 +6356,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>2</v>
@@ -6313,13 +6370,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6327,10 +6384,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>6</v>
@@ -6344,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>16</v>
@@ -6359,7 +6416,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>3</v>
@@ -6379,7 +6436,7 @@
         <v>16</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6390,7 +6447,7 @@
         <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>3</v>
@@ -6404,13 +6461,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6418,10 +6475,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>3</v>
@@ -6435,13 +6492,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>312</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6449,10 +6506,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>1</v>
@@ -6466,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>16</v>
@@ -6478,10 +6535,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>2</v>
@@ -6495,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>16</v>
@@ -6507,10 +6564,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
@@ -6524,13 +6581,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6538,10 +6595,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>1</v>
@@ -6555,13 +6612,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6569,16 +6626,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="15" t="n">
@@ -6586,13 +6643,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6600,10 +6657,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>1</v>
@@ -6619,13 +6676,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6633,10 +6690,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1</v>
@@ -6650,13 +6707,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6664,10 +6721,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>7</v>
@@ -6681,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>16</v>
@@ -6696,7 +6753,7 @@
         <v>155</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>7</v>
@@ -6710,13 +6767,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6724,10 +6781,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>3</v>
@@ -6741,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>16</v>
@@ -6753,10 +6810,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>1</v>
@@ -6782,10 +6839,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1</v>
@@ -6799,13 +6856,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6813,16 +6870,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D24" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="15" t="n">
@@ -6830,13 +6887,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6847,7 +6904,7 @@
         <v>182</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D25" s="13" t="n">
         <v>1</v>
@@ -6861,13 +6918,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6878,7 +6935,7 @@
         <v>135</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>2</v>
@@ -6892,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>16</v>
@@ -6907,7 +6964,7 @@
         <v>117</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>2</v>
@@ -6921,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>16</v>
@@ -6933,10 +6990,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>1</v>
@@ -6950,18 +7007,18 @@
         <v>0</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G29" s="10" t="n">
         <f aca="false">SUMIFS(G5:G28,I5:I28,"확정")</f>
@@ -6970,7 +7027,7 @@
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G30" s="10" t="n">
         <f aca="false">SUM(G5:G28)</f>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -554,2577 +554,2577 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="16">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>3D프린팅 수동변속기 제작 - 구매 물품 목록 (v4.1)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="16">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다(비고의 검색어로 확인).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="16">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>품명</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>단가(원)</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>금액(원)</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="J4" s="30" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="5" ht="29.25" customHeight="1" s="16">
-      <c r="A5" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="A5" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>6001ZZ 볼 베어링 (10개 묶음)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>12×28×8</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>묶음</t>
         </is>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="33" t="n">
         <v>6000</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="34">
         <f>D5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>끝판 4 + 출력 기어 12 + 아이들러 2 + 클러치 파일럿 1 = 19개</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
         <is>
           <t>v3 단가 · 쿠팡 /vp/products/8630678241</t>
         </is>
       </c>
     </row>
     <row r="6" ht="29.25" customHeight="1" s="16">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>6003ZZ 볼 베어링</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>17×35×10</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="23">
+      <c r="D6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="34">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>클러치 릴리스 베어링</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J6" s="32" t="inlineStr">
         <is>
           <t>단가 미확인 · 검색어 "6003ZZ" · 02 시험편으로 압입 자리 확인</t>
         </is>
       </c>
     </row>
     <row r="7" ht="29.25" customHeight="1" s="16">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>연마봉(강철 축)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Ø12 1m → 435·358(둘 다 전체 양면 D컷: 마주 보는 두 면, 면 사이 10.0) + 160</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="n">
+      <c r="D7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="n">
         <v>16000</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="34">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>입력축 435, 출력축 358, 레버봉 160</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J7" s="32" t="inlineStr">
         <is>
           <t>v3 단가 · 소망트레이딩 · 절단·양면 D컷 비용 미확인(전화 문의)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="29.25" customHeight="1" s="16">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>연마봉(강철 축) 짧은 것</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Ø12, 55mm 이상 (55로 절단)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="23">
+      <c r="D8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="34">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>후진 아이들러 축</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J8" s="32" t="inlineStr">
         <is>
           <t>1m 에서 위 3개를 자르면 약 41mm 만 남아 따로 필요 · 단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="9" ht="29.25" customHeight="1" s="16">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>연마봉(변속 레일)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>Ø6, 371mm</t>
         </is>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="23">
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="n"/>
+      <c r="G9" s="34">
         <f>D9*F9</f>
         <v/>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>시프트 레일</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J9" s="32" t="inlineStr">
         <is>
           <t>소망트레이딩 · 단가 미확인 (v3 참고: 200mm 2,600원)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="29.25" customHeight="1" s="16">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>강철 평행핀</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>Ø5×25</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="23">
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="n"/>
+      <c r="G10" s="34">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>출력 기어 6개 × 4 = 24 (+여유 4): 도그</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J10" s="32" t="inlineStr">
         <is>
           <t>검색어 "평행핀 5x25" · 02 시험편(구멍 4.8/4.9/5.0)으로 압입 구멍 확정</t>
         </is>
       </c>
     </row>
     <row r="11" ht="29.25" customHeight="1" s="16">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>강철 평행핀</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>Ø5×40</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="23">
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="n"/>
+      <c r="G11" s="34">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>스프로킷 커플링 핀</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J11" s="32" t="inlineStr">
         <is>
           <t>검색어 "평행핀 5x40"</t>
         </is>
       </c>
     </row>
     <row r="12" ht="29.25" customHeight="1" s="16">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>NBR 고무 호스</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>안지름 5 × 바깥지름 10</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="D12" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="23">
+      <c r="F12" s="33" t="n"/>
+      <c r="G12" s="34">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>핀 쿠션 (6mm × 24개 = 144mm)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J12" s="32" t="inlineStr">
         <is>
           <t>쇼어 70A 내외 · 검색어 "NBR 호스 5mm 10mm"</t>
         </is>
       </c>
     </row>
     <row r="13" ht="29.25" customHeight="1" s="16">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>큰 와셔 DIN9021 M16 (강철)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>안지름 17 × 바깥지름 50 × 두께 3</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="23">
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="n"/>
+      <c r="G13" s="34">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>클러치 원판 1 + 여분 1</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J13" s="32" t="inlineStr">
         <is>
           <t>검색어 "M16 큰와셔 50mm" · 두께 3 확인</t>
         </is>
       </c>
     </row>
     <row r="14" ht="29.25" customHeight="1" s="16">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>코르크 시트</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>두께 2mm, A4</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="D14" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>장</t>
         </is>
       </c>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="23">
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="34">
         <f>D14*F14</f>
         <v/>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>클러치 마찰재 링 2개 (바깥 Ø50, 안 Ø26)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr">
         <is>
           <t>검색어 "코르크 시트 2mm"</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29.25" customHeight="1" s="16">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>압축 스프링 C252</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>외경 18, 자유장 32</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="n">
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="n">
         <v>8360</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="34">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>포크 카트리지 3 + 클러치 3 + 레버 후진 잠금 1</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="inlineStr">
         <is>
           <t>디바이스마트 no=15336269 · 선경 미표기 → 스프링 상수·허용 하중으로 역산 선경 약 1.4~1.6, 안지름 약 14.8~15.2 (필요 12.5 이상, 미검증)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="29.25" customHeight="1" s="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>압축 스프링 C147</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>외경 5, 길이 10</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="n">
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="n">
         <v>990</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="34">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>러그 디텐트</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr">
         <is>
           <t>디바이스마트 no=15336164</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29.25" customHeight="1" s="16">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>강구</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Ø6mm 50개</t>
         </is>
       </c>
-      <c r="D17" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="D17" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>봉</t>
         </is>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="33" t="n">
         <v>3500</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="34">
         <f>D17*F17</f>
         <v/>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>러그 디텐트 3</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J17" s="32" t="inlineStr">
         <is>
           <t>v3 단가 · 쿠팡 /9638493021</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29.25" customHeight="1" s="16">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>샤프트 칼라 (Ø6 축용)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>안지름 6, 바깥지름 12, 폭 8, 멈춤나사형 (표준 규격)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="23">
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="34">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>변속 레일 카트리지 양쪽</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J18" s="32" t="inlineStr">
         <is>
           <t>예: RS PRO 8236939 (6/12/8, 5개 묶음) · 바깥지름 12 넘으면 카트리지 구멍(13)에 안 들어감</t>
         </is>
       </c>
     </row>
     <row r="19" ht="29.25" customHeight="1" s="16">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>볼트너트 세트</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>M3·M4·M5 스텐 500pcs</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="D19" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F19" s="22" t="n">
+      <c r="F19" s="33" t="n">
         <v>12580</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="34">
         <f>D19*F19</f>
         <v/>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>일반 고정</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J19" s="32" t="inlineStr">
         <is>
           <t>v3 단가 · 쿠팡 /2236695303 · 길이 구성 미확인 → 아래 길이별 항목과 비교 후 부족분만</t>
         </is>
       </c>
     </row>
     <row r="20" ht="29.25" customHeight="1" s="16">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>M3 볼트 + 너트</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>M3×20</t>
         </is>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="23">
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="34">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="32" t="inlineStr">
         <is>
           <t>슬리브 결합 (머리·너트는 육각 자리 안에 숨음)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J20" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="21" ht="29.25" customHeight="1" s="16">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>M3 볼트</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>M3×30</t>
         </is>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="23">
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="34">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>러그 (자가탭, 끝이 레일을 누름)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="22" ht="29.25" customHeight="1" s="16">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>M3 볼트</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>M3×12</t>
         </is>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="23">
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="34">
         <f>D22*F22</f>
         <v/>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>칼라 7, 디텐트 3, 클러치 덮개 7, 축 끝 덮개 4, 바퀴 덮개 2, 아크릴 14</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J22" s="32" t="inlineStr">
         <is>
           <t>모두 자가탭 · 아크릴에는 M3 와셔</t>
         </is>
       </c>
     </row>
     <row r="23" ht="29.25" customHeight="1" s="16">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>M3 볼트</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
         <is>
           <t>M3×16</t>
         </is>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="23">
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="n"/>
+      <c r="G23" s="34">
         <f>D23*F23</f>
         <v/>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="32" t="inlineStr">
         <is>
           <t>바퀴 덮개 아래 받침</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J23" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="24" ht="29.25" customHeight="1" s="16">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>M3 볼트</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>M3×50</t>
         </is>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="23">
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="34">
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>끝 채움판 → 끝판</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J24" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="25" ht="29.25" customHeight="1" s="16">
-      <c r="A25" s="20" t="n">
+      <c r="A25" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>M3 볼트</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>M3×8 6개 + M3×10 1개</t>
         </is>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="23">
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="n"/>
+      <c r="G25" s="34">
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="32" t="inlineStr">
         <is>
           <t>포크 카트리지 뚜껑 6, 클러치 포크 속선 누름 1</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J25" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="26" ht="29.25" customHeight="1" s="16">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>M3 무두볼트</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>M3×8</t>
         </is>
       </c>
-      <c r="D26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="23">
+      <c r="D26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="34">
         <f>D26*F26</f>
         <v/>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="32" t="inlineStr">
         <is>
           <t>표시 바퀴 고정</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="I26" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J26" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="27" ht="29.25" customHeight="1" s="16">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>M3 평와셔</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>M3 (바깥지름 7 내외)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="23">
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="34">
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="32" t="inlineStr">
         <is>
           <t>아크릴 고정 나사 밑 (아크릴 균열 방지)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J27" s="32" t="inlineStr">
         <is>
           <t>볼트너트 세트에 있으면 생략</t>
         </is>
       </c>
     </row>
     <row r="28" ht="29.25" customHeight="1" s="16">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>M4 볼트 + 너트</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>M4×30</t>
         </is>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="23">
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="34">
         <f>D28*F28</f>
         <v/>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="32" t="inlineStr">
         <is>
           <t>케이지 4, 피벗 8, 게이트 4, 받침 브래킷 4</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J28" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="29" ht="29.25" customHeight="1" s="16">
-      <c r="A29" s="20" t="n">
+      <c r="A29" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>M4 볼트 + 너트</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>M4×16</t>
         </is>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="23">
+      <c r="F29" s="33" t="n"/>
+      <c r="G29" s="34">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>클러치 포크 브래킷 4, 페달 발판 4</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J29" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="30" ht="29.25" customHeight="1" s="16">
-      <c r="A30" s="20" t="n">
+      <c r="A30" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>M4 볼트 + 너트</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>M4×60</t>
         </is>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="23">
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="34">
         <f>D30*F30</f>
         <v/>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>클러치 기둥</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J30" s="21" t="inlineStr">
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J30" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="31" ht="29.25" customHeight="1" s="16">
-      <c r="A31" s="20" t="n">
+      <c r="A31" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>M5 볼트 + 너트</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>M5×10</t>
         </is>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="23">
+      <c r="F31" s="33" t="n"/>
+      <c r="G31" s="34">
         <f>D31*F31</f>
         <v/>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr">
         <is>
           <t>클러치 조절나사 (끝까지 조임 = 설정)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J31" s="21" t="inlineStr">
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J31" s="32" t="inlineStr">
         <is>
           <t>M5×12 이상 금지 (미끄럼 토크가 1.05N·m 까지 올라가 기어 설계 하중 초과)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="29.25" customHeight="1" s="16">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>M5 볼트 + 너트</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>M5×20</t>
         </is>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="23">
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="34">
         <f>D32*F32</f>
         <v/>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>클러치 릴리스 누름 볼트</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="inlineStr">
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J32" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="33" ht="29.25" customHeight="1" s="16">
-      <c r="A33" s="20" t="n">
+      <c r="A33" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>M5 볼트 + 나일론 너트</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>M5×35</t>
         </is>
       </c>
-      <c r="D33" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="D33" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="23">
+      <c r="F33" s="33" t="n"/>
+      <c r="G33" s="34">
         <f>D33*F33</f>
         <v/>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="32" t="inlineStr">
         <is>
           <t>클러치 포크 피벗</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J33" s="21" t="inlineStr">
+      <c r="I33" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J33" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="34" ht="29.25" customHeight="1" s="16">
-      <c r="A34" s="20" t="n">
+      <c r="A34" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>M6 볼트·너트</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>M6×50 10개 + 너트 10개</t>
         </is>
       </c>
-      <c r="D34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="D34" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F34" s="22" t="n">
+      <c r="F34" s="33" t="n">
         <v>4500</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="34">
         <f>D34*F34</f>
         <v/>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>페달 힌지 2 (남는 너트 4개는 모터 받침에 씀)</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="I34" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J34" s="32" t="inlineStr">
         <is>
           <t>v3 단가 · 쿠팡 /9679379731</t>
         </is>
       </c>
     </row>
     <row r="35" ht="29.25" customHeight="1" s="16">
-      <c r="A35" s="20" t="n">
+      <c r="A35" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>M6 볼트</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>M6×25</t>
         </is>
       </c>
-      <c r="D35" s="20" t="n">
+      <c r="D35" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="23">
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="34">
         <f>D35*F35</f>
         <v/>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="32" t="inlineStr">
         <is>
           <t>모터 받침: K9B 브래킷 바닥 → 45 받침대 밑면 너트</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J35" s="21" t="inlineStr">
+      <c r="I35" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J35" s="32" t="inlineStr">
         <is>
           <t>M6×30 이상 금지 (MDF 에 닿음) · 단가 미확인</t>
         </is>
       </c>
     </row>
     <row r="36" ht="29.25" customHeight="1" s="16">
-      <c r="A36" s="20" t="n">
+      <c r="A36" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>목재 나사</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>4×20</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="n">
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>4×16</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="23">
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="34">
         <f>D36*F36</f>
         <v/>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>받침 브래킷 8, 클러치 덮개 4, 모터 받침 4, 페달 받침 8</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J36" s="21" t="inlineStr">
+      <c r="I36" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J36" s="32" t="inlineStr">
+        <is>
+          <t>MDF 12T 에 10~11 박힘 · 4×20 이상은 밑으로 나옴 · 단가 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="29.25" customHeight="1" s="16">
+      <c r="A37" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>에폭시 접착제</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>2액형</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F37" s="33" t="n"/>
+      <c r="G37" s="34">
+        <f>D37*F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="32" t="inlineStr">
+        <is>
+          <t>레버봉-핑거·손잡이, 아이들러 축, 클러치 와셔-허브, 고무 쿠션</t>
+        </is>
+      </c>
+      <c r="I37" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J37" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="29.25" customHeight="1" s="16">
-      <c r="A37" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>에폭시 접착제</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>2액형</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="23">
-        <f>D37*F37</f>
-        <v/>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>레버봉-핑거·손잡이, 아이들러 축, 클러치 와셔-허브, 고무 쿠션</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
+    <row r="38" ht="29.25" customHeight="1" s="16">
+      <c r="A38" s="31" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>순간접착제</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="34">
+        <f>D38*F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>덮개 스위치, 홀센서, 자석</t>
+        </is>
+      </c>
+      <c r="I38" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J38" s="32" t="inlineStr">
+        <is>
+          <t>보유하면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="29.25" customHeight="1" s="16">
+      <c r="A39" s="31" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>자전거 브레이크 케이블 세트</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>속선 + 아우터(바깥지름 5 내외)</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="n"/>
+      <c r="G39" s="34">
+        <f>D39*F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="32" t="inlineStr">
+        <is>
+          <t>클러치 페달 → 클러치 포크</t>
+        </is>
+      </c>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>아우터가 끝판 B 구멍 Ø6 에 들어가야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="29.25" customHeight="1" s="16">
+      <c r="A40" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>인장 스프링</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>선경 1.0 외경 7, 1m</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F40" s="33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G40" s="34">
+        <f>D40*F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>페달 복귀 (잘라 고리 만듦)</t>
+        </is>
+      </c>
+      <c r="I40" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J40" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /7939346368</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="29.25" customHeight="1" s="16">
+      <c r="A41" s="31" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>MDF 판</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>12T 300×1200 재단</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="32" t="inlineStr">
+        <is>
+          <t>장</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G41" s="34">
+        <f>D41*F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>바닥판 750×300 (모터·클러치 덮개 포함)</t>
+        </is>
+      </c>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J41" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /71452005</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="29.25" customHeight="1" s="16">
+      <c r="A42" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>투명 아크릴</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>A3 3T</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>장</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G42" s="34">
+        <f>D42*F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="32" t="inlineStr">
+        <is>
+          <t>덮개 윗판 250×321, 옆판 200×321 × 2</t>
+        </is>
+      </c>
+      <c r="I42" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J42" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /9593337115 · 재단 주문 가능하면 치수대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="29.25" customHeight="1" s="16">
+      <c r="A43" s="31" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>아두이노 레오나르도 R3 + 케이블</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>ATmega32u4</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F43" s="33" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G43" s="34">
+        <f>D43*F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="32" t="inlineStr">
+        <is>
+          <t>센서 → PC 게임 입력 + 모터 허가 출력</t>
+        </is>
+      </c>
+      <c r="I43" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J43" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /1119152790</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="29.25" customHeight="1" s="16">
+      <c r="A44" s="31" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>홀센서 A3144</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>3핀 소자</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F44" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="G44" s="34">
+        <f>D44*F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="32" t="inlineStr">
+        <is>
+          <t>기어 위치 6 + 출력 rpm 1</t>
+        </is>
+      </c>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J44" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /8520223332</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="29.25" customHeight="1" s="16">
+      <c r="A45" s="31" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>네오디뮴 자석</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Ø6×3mm 40개</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="32" t="inlineStr">
+        <is>
+          <t>봉</t>
+        </is>
+      </c>
+      <c r="F45" s="33" t="n">
+        <v>11300</v>
+      </c>
+      <c r="G45" s="34">
+        <f>D45*F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="32" t="inlineStr">
+        <is>
+          <t>러그 3 + 표시 바퀴 4</t>
+        </is>
+      </c>
+      <c r="I45" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J45" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /7119515778</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="29.25" customHeight="1" s="16">
+      <c r="A46" s="31" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>가변저항 B10K</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>노브 포함</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F46" s="33" t="n">
+        <v>500</v>
+      </c>
+      <c r="G46" s="34">
+        <f>D46*F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="32" t="inlineStr">
+        <is>
+          <t>핸들·클러치·브레이크</t>
+        </is>
+      </c>
+      <c r="I46" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J46" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 축 지름·반달 치수 미확인 (페달 팔 구멍 Ø6.1, 평면 4.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="29.25" customHeight="1" s="16">
+      <c r="A47" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>마이크로스위치</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>KW-11-3Z 레버형</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F47" s="33" t="n">
+        <v>400</v>
+      </c>
+      <c r="G47" s="34">
+        <f>D47*F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="32" t="inlineStr">
+        <is>
+          <t>덮개 열림 감지 1 + 여분 1</t>
+        </is>
+      </c>
+      <c r="I47" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J47" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /9167678186</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="29.25" customHeight="1" s="16">
+      <c r="A48" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>점퍼 케이블</t>
+        </is>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>M-F 40P 40cm</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F48" s="33" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G48" s="34">
+        <f>D48*F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="32" t="inlineStr">
+        <is>
+          <t>센서 배선</t>
+        </is>
+      </c>
+      <c r="I48" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J48" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /9699042565</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="29.25" customHeight="1" s="16">
+      <c r="A49" s="31" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>만능기판</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>20개 묶음</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="32" t="inlineStr">
+        <is>
+          <t>봉</t>
+        </is>
+      </c>
+      <c r="F49" s="33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G49" s="34">
+        <f>D49*F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="32" t="inlineStr">
+        <is>
+          <t>센서 배선</t>
+        </is>
+      </c>
+      <c r="I49" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J49" s="32" t="inlineStr">
+        <is>
+          <t>v3 단가 · 쿠팡 /9661304796</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="29.25" customHeight="1" s="16">
+      <c r="A50" s="31" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>자동차 릴레이 + 소켓</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>12V, 접점 40A, 4핀</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F50" s="33" t="n"/>
+      <c r="G50" s="34">
+        <f>D50*F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="32" t="inlineStr">
+        <is>
+          <t>모터 전원 주 스위치</t>
+        </is>
+      </c>
+      <c r="I50" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J50" s="32" t="inlineStr">
+        <is>
+          <t>검색어 "12V 40A 릴레이 소켓" · 코일 회로에 비상정지·덮개 스위치·5V 릴레이 모듈 직렬</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="29.25" customHeight="1" s="16">
+      <c r="A51" s="31" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>블레이드 퓨즈 + 인라인 홀더</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>15A</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F51" s="33" t="n"/>
+      <c r="G51" s="34">
+        <f>D51*F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="32" t="inlineStr">
+        <is>
+          <t>배터리 + 단자 바로 옆</t>
+        </is>
+      </c>
+      <c r="I51" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J51" s="32" t="inlineStr">
+        <is>
+          <t>여분 퓨즈 2개 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="29.25" customHeight="1" s="16">
+      <c r="A52" s="31" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>비상정지 스위치</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>버섯형, b접점(NC)</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F52" s="33" t="n"/>
+      <c r="G52" s="34">
+        <f>D52*F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="32" t="inlineStr">
+        <is>
+          <t>운영자 비상 차단 (릴레이 코일 회로)</t>
+        </is>
+      </c>
+      <c r="I52" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J52" s="32" t="inlineStr">
         <is>
           <t>단가 미확인</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="29.25" customHeight="1" s="16">
-      <c r="A38" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>순간접착제</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="23">
-        <f>D38*F38</f>
-        <v/>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>덮개 스위치, 홀센서, 자석</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J38" s="21" t="inlineStr">
+    <row r="53" ht="29.25" customHeight="1" s="16">
+      <c r="A53" s="31" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>5V 릴레이 모듈</t>
+        </is>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>1채널</t>
+        </is>
+      </c>
+      <c r="D53" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F53" s="33" t="n"/>
+      <c r="G53" s="34">
+        <f>D53*F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="32" t="inlineStr">
+        <is>
+          <t>아두이노 워치독 → 주 릴레이 코일 차단</t>
+        </is>
+      </c>
+      <c r="I53" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J53" s="32" t="inlineStr">
+        <is>
+          <t>로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="29.25" customHeight="1" s="16">
+      <c r="A54" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>다이오드 1N4007</t>
+        </is>
+      </c>
+      <c r="C54" s="31" t="inlineStr"/>
+      <c r="D54" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F54" s="33" t="n"/>
+      <c r="G54" s="34">
+        <f>D54*F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="32" t="inlineStr">
+        <is>
+          <t>주 릴레이 코일 역기전력 흡수 1 + 여분 1</t>
+        </is>
+      </c>
+      <c r="I54" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J54" s="32" t="inlineStr">
+        <is>
+          <t>내장 다이오드 릴레이면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="29.25" customHeight="1" s="16">
+      <c r="A55" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>전선</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>1.5mm² 이상, 적·흑 각 2m</t>
+        </is>
+      </c>
+      <c r="D55" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="32" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F55" s="33" t="n"/>
+      <c r="G55" s="34">
+        <f>D55*F55</f>
+        <v/>
+      </c>
+      <c r="H55" s="32" t="inlineStr">
+        <is>
+          <t>배터리-퓨즈-릴레이-모터 드라이버</t>
+        </is>
+      </c>
+      <c r="I55" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J55" s="32" t="inlineStr">
+        <is>
+          <t>퓨즈 15A 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="29.25" customHeight="1" s="16">
+      <c r="A56" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>압착 단자 세트</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>250 규격(6.3mm) 절연 암 평형 단자 + 수축 튜브</t>
+        </is>
+      </c>
+      <c r="D56" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="32" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F56" s="33" t="n"/>
+      <c r="G56" s="34">
+        <f>D56*F56</f>
+        <v/>
+      </c>
+      <c r="H56" s="32" t="inlineStr">
+        <is>
+          <t>퓨즈 홀더·릴레이 소켓 연결 (배터리 쪽은 키트 선 단자 재사용)</t>
+        </is>
+      </c>
+      <c r="I56" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J56" s="32" t="inlineStr">
+        <is>
+          <t>배터리 단자 = 6.3mm 평형 탭(사진 확인) · 홀더·소켓에 단자 포함이면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="29.25" customHeight="1" s="16">
+      <c r="A57" s="31" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>저항</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>10kΩ 1개 + 4.7kΩ 1개 (1/4W)</t>
+        </is>
+      </c>
+      <c r="D57" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="32" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F57" s="33" t="n"/>
+      <c r="G57" s="34">
+        <f>D57*F57</f>
+        <v/>
+      </c>
+      <c r="H57" s="32" t="inlineStr">
+        <is>
+          <t>안전 회로 감지 (비상정지·덮개 뒤 12V → 아두이노 A4)</t>
+        </is>
+      </c>
+      <c r="I57" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J57" s="32" t="inlineStr">
+        <is>
+          <t>풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="29.25" customHeight="1" s="16">
+      <c r="A58" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>PLA 필라멘트</t>
+        </is>
+      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>2.85mm, 1kg 롤</t>
+        </is>
+      </c>
+      <c r="D58" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="32" t="inlineStr">
+        <is>
+          <t>롤</t>
+        </is>
+      </c>
+      <c r="F58" s="33" t="n"/>
+      <c r="G58" s="34">
+        <f>D58*F58</f>
+        <v/>
+      </c>
+      <c r="H58" s="32" t="inlineStr">
+        <is>
+          <t>출력 예상 4.03kg + 실패 여유 15% − 보유 750g 롤 1개</t>
+        </is>
+      </c>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J58" s="32" t="inlineStr">
+        <is>
+          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 단가 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="29.25" customHeight="1" s="16">
+      <c r="A59" s="31" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="32" t="inlineStr">
+        <is>
+          <t>걸이 저울</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>0~5kg, 10g 단위</t>
+        </is>
+      </c>
+      <c r="D59" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F59" s="33" t="n"/>
+      <c r="G59" s="34">
+        <f>D59*F59</f>
+        <v/>
+      </c>
+      <c r="H59" s="32" t="inlineStr">
+        <is>
+          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
+        </is>
+      </c>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="J59" s="32" t="inlineStr">
         <is>
           <t>보유하면 생략</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="29.25" customHeight="1" s="16">
-      <c r="A39" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="21" t="inlineStr">
-        <is>
-          <t>자전거 브레이크 케이블 세트</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
-        <is>
-          <t>속선 + 아우터(바깥지름 5 내외)</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="23">
-        <f>D39*F39</f>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="inlineStr">
-        <is>
-          <t>클러치 페달 → 클러치 포크</t>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J39" s="21" t="inlineStr">
-        <is>
-          <t>아우터가 끝판 B 구멍 Ø6 에 들어가야 함</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="29.25" customHeight="1" s="16">
-      <c r="A40" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>인장 스프링</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>선경 1.0 외경 7, 1m</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F40" s="22" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G40" s="23">
-        <f>D40*F40</f>
-        <v/>
-      </c>
-      <c r="H40" s="21" t="inlineStr">
-        <is>
-          <t>페달 복귀 (잘라 고리 만듦)</t>
-        </is>
-      </c>
-      <c r="I40" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J40" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /7939346368</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="29.25" customHeight="1" s="16">
-      <c r="A41" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t>MDF 판</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="inlineStr">
-        <is>
-          <t>12T 300×1200 재단</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>장</t>
-        </is>
-      </c>
-      <c r="F41" s="22" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G41" s="23">
-        <f>D41*F41</f>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="inlineStr">
-        <is>
-          <t>바닥판 750×300 (모터·클러치 덮개 포함)</t>
-        </is>
-      </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J41" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /71452005</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="29.25" customHeight="1" s="16">
-      <c r="A42" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>투명 아크릴</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>A3 3T</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>장</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G42" s="23">
-        <f>D42*F42</f>
-        <v/>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>덮개 윗판 250×321, 옆판 200×321 × 2</t>
-        </is>
-      </c>
-      <c r="I42" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J42" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /9593337115 · 재단 주문 가능하면 치수대로</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="29.25" customHeight="1" s="16">
-      <c r="A43" s="20" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>아두이노 레오나르도 R3 + 케이블</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>ATmega32u4</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F43" s="22" t="n">
-        <v>9200</v>
-      </c>
-      <c r="G43" s="23">
-        <f>D43*F43</f>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="inlineStr">
-        <is>
-          <t>센서 → PC 게임 입력 + 모터 허가 출력</t>
-        </is>
-      </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J43" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /1119152790</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="29.25" customHeight="1" s="16">
-      <c r="A44" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="21" t="inlineStr">
-        <is>
-          <t>홀센서 A3144</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>3핀 소자</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="n">
-        <v>90</v>
-      </c>
-      <c r="G44" s="23">
-        <f>D44*F44</f>
-        <v/>
-      </c>
-      <c r="H44" s="21" t="inlineStr">
-        <is>
-          <t>기어 위치 6 + 출력 rpm 1</t>
-        </is>
-      </c>
-      <c r="I44" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J44" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /8520223332</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="29.25" customHeight="1" s="16">
-      <c r="A45" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>네오디뮴 자석</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>Ø6×3mm 40개</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>봉</t>
-        </is>
-      </c>
-      <c r="F45" s="22" t="n">
-        <v>11300</v>
-      </c>
-      <c r="G45" s="23">
-        <f>D45*F45</f>
-        <v/>
-      </c>
-      <c r="H45" s="21" t="inlineStr">
-        <is>
-          <t>러그 3 + 표시 바퀴 4</t>
-        </is>
-      </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J45" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /7119515778</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="29.25" customHeight="1" s="16">
-      <c r="A46" s="20" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="21" t="inlineStr">
-        <is>
-          <t>가변저항 B10K</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>노브 포함</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F46" s="22" t="n">
-        <v>500</v>
-      </c>
-      <c r="G46" s="23">
-        <f>D46*F46</f>
-        <v/>
-      </c>
-      <c r="H46" s="21" t="inlineStr">
-        <is>
-          <t>핸들·클러치·브레이크</t>
-        </is>
-      </c>
-      <c r="I46" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J46" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 축 지름·반달 치수 미확인 (페달 팔 구멍 Ø6.1, 평면 4.6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="29.25" customHeight="1" s="16">
-      <c r="A47" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="21" t="inlineStr">
-        <is>
-          <t>마이크로스위치</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>KW-11-3Z 레버형</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F47" s="22" t="n">
-        <v>400</v>
-      </c>
-      <c r="G47" s="23">
-        <f>D47*F47</f>
-        <v/>
-      </c>
-      <c r="H47" s="21" t="inlineStr">
-        <is>
-          <t>덮개 열림 감지 1 + 여분 1</t>
-        </is>
-      </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J47" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /9167678186</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="29.25" customHeight="1" s="16">
-      <c r="A48" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="21" t="inlineStr">
-        <is>
-          <t>점퍼 케이블</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>M-F 40P 40cm</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F48" s="22" t="n">
-        <v>5300</v>
-      </c>
-      <c r="G48" s="23">
-        <f>D48*F48</f>
-        <v/>
-      </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>센서 배선</t>
-        </is>
-      </c>
-      <c r="I48" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J48" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /9699042565</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="29.25" customHeight="1" s="16">
-      <c r="A49" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="21" t="inlineStr">
-        <is>
-          <t>만능기판</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>20개 묶음</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="21" t="inlineStr">
-        <is>
-          <t>봉</t>
-        </is>
-      </c>
-      <c r="F49" s="22" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G49" s="23">
-        <f>D49*F49</f>
-        <v/>
-      </c>
-      <c r="H49" s="21" t="inlineStr">
-        <is>
-          <t>센서 배선</t>
-        </is>
-      </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J49" s="21" t="inlineStr">
-        <is>
-          <t>v3 단가 · 쿠팡 /9661304796</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="29.25" customHeight="1" s="16">
-      <c r="A50" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>자동차 릴레이 + 소켓</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>12V, 접점 40A, 4핀</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F50" s="22" t="n"/>
-      <c r="G50" s="23">
-        <f>D50*F50</f>
-        <v/>
-      </c>
-      <c r="H50" s="21" t="inlineStr">
-        <is>
-          <t>모터 전원 주 스위치</t>
-        </is>
-      </c>
-      <c r="I50" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J50" s="21" t="inlineStr">
-        <is>
-          <t>검색어 "12V 40A 릴레이 소켓" · 코일 회로에 비상정지·덮개 스위치·5V 릴레이 모듈 직렬</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="29.25" customHeight="1" s="16">
-      <c r="A51" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="21" t="inlineStr">
-        <is>
-          <t>블레이드 퓨즈 + 인라인 홀더</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
-        <is>
-          <t>15A</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="21" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F51" s="22" t="n"/>
-      <c r="G51" s="23">
-        <f>D51*F51</f>
-        <v/>
-      </c>
-      <c r="H51" s="21" t="inlineStr">
-        <is>
-          <t>배터리 + 단자 바로 옆</t>
-        </is>
-      </c>
-      <c r="I51" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J51" s="21" t="inlineStr">
-        <is>
-          <t>여분 퓨즈 2개 권장</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="29.25" customHeight="1" s="16">
-      <c r="A52" s="20" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="21" t="inlineStr">
-        <is>
-          <t>비상정지 스위치</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>버섯형, b접점(NC)</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F52" s="22" t="n"/>
-      <c r="G52" s="23">
-        <f>D52*F52</f>
-        <v/>
-      </c>
-      <c r="H52" s="21" t="inlineStr">
-        <is>
-          <t>운영자 비상 차단 (릴레이 코일 회로)</t>
-        </is>
-      </c>
-      <c r="I52" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J52" s="21" t="inlineStr">
-        <is>
-          <t>단가 미확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="29.25" customHeight="1" s="16">
-      <c r="A53" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>5V 릴레이 모듈</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>1채널</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F53" s="22" t="n"/>
-      <c r="G53" s="23">
-        <f>D53*F53</f>
-        <v/>
-      </c>
-      <c r="H53" s="21" t="inlineStr">
-        <is>
-          <t>아두이노 워치독 → 주 릴레이 코일 차단</t>
-        </is>
-      </c>
-      <c r="I53" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J53" s="21" t="inlineStr">
-        <is>
-          <t>로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="29.25" customHeight="1" s="16">
-      <c r="A54" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="21" t="inlineStr">
-        <is>
-          <t>다이오드 1N4007</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr"/>
-      <c r="D54" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F54" s="22" t="n"/>
-      <c r="G54" s="23">
-        <f>D54*F54</f>
-        <v/>
-      </c>
-      <c r="H54" s="21" t="inlineStr">
-        <is>
-          <t>주 릴레이 코일 역기전력 흡수 1 + 여분 1</t>
-        </is>
-      </c>
-      <c r="I54" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J54" s="21" t="inlineStr">
-        <is>
-          <t>내장 다이오드 릴레이면 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="29.25" customHeight="1" s="16">
-      <c r="A55" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="21" t="inlineStr">
-        <is>
-          <t>전선</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>1.5mm² 이상, 적·흑 각 2m</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F55" s="22" t="n"/>
-      <c r="G55" s="23">
-        <f>D55*F55</f>
-        <v/>
-      </c>
-      <c r="H55" s="21" t="inlineStr">
-        <is>
-          <t>배터리-퓨즈-릴레이-모터 드라이버</t>
-        </is>
-      </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J55" s="21" t="inlineStr">
-        <is>
-          <t>퓨즈 15A 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="29.25" customHeight="1" s="16">
-      <c r="A56" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="21" t="inlineStr">
-        <is>
-          <t>압착 단자 세트</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>250 규격(6.3mm) 절연 암 평형 단자 + 수축 튜브</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="21" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F56" s="22" t="n"/>
-      <c r="G56" s="23">
-        <f>D56*F56</f>
-        <v/>
-      </c>
-      <c r="H56" s="21" t="inlineStr">
-        <is>
-          <t>퓨즈 홀더·릴레이 소켓 연결 (배터리 쪽은 키트 선 단자 재사용)</t>
-        </is>
-      </c>
-      <c r="I56" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J56" s="21" t="inlineStr">
-        <is>
-          <t>배터리 단자 = 6.3mm 평형 탭(사진 확인) · 홀더·소켓에 단자 포함이면 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="29.25" customHeight="1" s="16">
-      <c r="A57" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="21" t="inlineStr">
-        <is>
-          <t>저항</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>10kΩ 1개 + 4.7kΩ 1개 (1/4W)</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="21" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="23">
-        <f>D57*F57</f>
-        <v/>
-      </c>
-      <c r="H57" s="21" t="inlineStr">
-        <is>
-          <t>안전 회로 감지 (비상정지·덮개 뒤 12V → 아두이노 A4)</t>
-        </is>
-      </c>
-      <c r="I57" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J57" s="21" t="inlineStr">
-        <is>
-          <t>풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="29.25" customHeight="1" s="16">
-      <c r="A58" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="21" t="inlineStr">
-        <is>
-          <t>PLA 필라멘트</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>2.85mm, 1kg 롤</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" s="21" t="inlineStr">
-        <is>
-          <t>롤</t>
-        </is>
-      </c>
-      <c r="F58" s="22" t="n"/>
-      <c r="G58" s="23">
-        <f>D58*F58</f>
-        <v/>
-      </c>
-      <c r="H58" s="21" t="inlineStr">
-        <is>
-          <t>출력 예상 4.03kg + 실패 여유 15% − 보유 750g 롤 1개</t>
-        </is>
-      </c>
-      <c r="I58" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J58" s="21" t="inlineStr">
-        <is>
-          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 단가 미확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="29.25" customHeight="1" s="16">
-      <c r="A59" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="21" t="inlineStr">
-        <is>
-          <t>걸이 저울</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>0~5kg, 10g 단위</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="n"/>
-      <c r="G59" s="23">
-        <f>D59*F59</f>
-        <v/>
-      </c>
-      <c r="H59" s="21" t="inlineStr">
-        <is>
-          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
-        </is>
-      </c>
-      <c r="I59" s="21" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr">
+    <row r="60" ht="29.25" customHeight="1" s="16">
+      <c r="A60" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>디지털 캘리퍼스</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>0.01mm 표시, 150mm</t>
+        </is>
+      </c>
+      <c r="D60" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F60" s="33" t="n"/>
+      <c r="G60" s="34">
+        <f>D60*F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="32" t="inlineStr">
+        <is>
+          <t>쿠폰·핀 구멍·축 지름 확인</t>
+        </is>
+      </c>
+      <c r="I60" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J60" s="32" t="inlineStr">
         <is>
           <t>보유하면 생략</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="29.25" customHeight="1" s="16">
-      <c r="A60" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="21" t="inlineStr">
-        <is>
-          <t>디지털 캘리퍼스</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>0.01mm 표시, 150mm</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="21" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="n"/>
-      <c r="G60" s="23">
-        <f>D60*F60</f>
-        <v/>
-      </c>
-      <c r="H60" s="21" t="inlineStr">
-        <is>
-          <t>쿠폰·핀 구멍·축 지름 확인</t>
-        </is>
-      </c>
-      <c r="I60" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J60" s="21" t="inlineStr">
-        <is>
-          <t>보유하면 생략</t>
-        </is>
-      </c>
-    </row>
     <row r="61" ht="29.25" customHeight="1" s="16">
-      <c r="A61" s="20" t="n">
+      <c r="A61" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="21" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>배송비</t>
         </is>
       </c>
-      <c r="C61" s="20" t="inlineStr">
+      <c r="C61" s="31" t="inlineStr">
         <is>
           <t>새 판매처 포함</t>
         </is>
       </c>
-      <c r="D61" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="21" t="inlineStr">
+      <c r="D61" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="32" t="inlineStr">
         <is>
           <t>식</t>
         </is>
       </c>
-      <c r="F61" s="22" t="n"/>
-      <c r="G61" s="23">
+      <c r="F61" s="33" t="n"/>
+      <c r="G61" s="34">
         <f>D61*F61</f>
         <v/>
       </c>
-      <c r="H61" s="21" t="n"/>
-      <c r="I61" s="21" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J61" s="21" t="inlineStr">
+      <c r="H61" s="32" t="n"/>
+      <c r="I61" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J61" s="32" t="inlineStr">
         <is>
           <t>v3 는 22,900원 · 새 항목 판매처에 따라 달라짐 (미확인)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>합계 (확정 항목, 단가 입력된 것만)</t>
         </is>
       </c>
-      <c r="G62" s="25">
+      <c r="G62" s="39">
         <f>SUMIFS(G5:G61,I5:I61,"확정")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B63" s="38" t="inlineStr">
         <is>
           <t>합계 (선택 포함)</t>
         </is>
       </c>
-      <c r="G63" s="25">
+      <c r="G63" s="39">
         <f>SUM(G5:G61)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="38" t="inlineStr">
         <is>
           <t>단가 미확인 항목 수</t>
         </is>
       </c>
-      <c r="G64" s="26">
+      <c r="G64" s="40">
         <f>COUNTBLANK(F5:F61)</f>
         <v/>
       </c>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D15" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H15" s="32" t="inlineStr">
         <is>
-          <t>포크 카트리지 3 + 클러치 3 + 레버 후진 잠금 1</t>
+          <t>포크 카트리지 3 + 클러치 3 + 레버 후진 잠금 1 + 페달 복귀 2</t>
         </is>
       </c>
       <c r="I15" s="32" t="inlineStr">
@@ -1237,32 +1237,30 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>볼트너트 세트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>M3·M4·M5 스텐 500pcs</t>
+          <t>M3×8 (육각 홈붙이, 스텐)</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>12580</v>
-      </c>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="n"/>
       <c r="G19" s="34">
         <f>D19*F19</f>
         <v/>
       </c>
       <c r="H19" s="32" t="inlineStr">
         <is>
-          <t>일반 고정</t>
+          <t>포크 카트리지 뚜껑 6, 디텐트 3 (C147 을 5mm 로 누름)</t>
         </is>
       </c>
       <c r="I19" s="32" t="inlineStr">
@@ -1272,7 +1270,7 @@
       </c>
       <c r="J19" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /2236695303 · 길이 구성 미확인 → 아래 길이별 항목과 비교 후 부족분만</t>
+          <t>모든 볼트는 렌치볼트(머리 Ø5.5): 부품의 머리 자리가 이 크기 · 단가 미확인</t>
         </is>
       </c>
     </row>
@@ -1282,20 +1280,20 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>M3 볼트 + 너트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>M3×20</t>
+          <t>M3×10</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F20" s="33" t="n"/>
@@ -1305,7 +1303,7 @@
       </c>
       <c r="H20" s="32" t="inlineStr">
         <is>
-          <t>슬리브 결합 (머리·너트는 육각 자리 안에 숨음)</t>
+          <t>클러치 포크 속선 누름 (자가탭, 와셔 1)</t>
         </is>
       </c>
       <c r="I20" s="32" t="inlineStr">
@@ -1325,16 +1323,16 @@
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>M3 볼트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>M3×30</t>
+          <t>M3×12</t>
         </is>
       </c>
       <c r="D21" s="31" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -1348,7 +1346,7 @@
       </c>
       <c r="H21" s="32" t="inlineStr">
         <is>
-          <t>러그 (자가탭, 끝이 레일을 누름)</t>
+          <t>칼라 7, 클러치 덮개 7, 축 끝 덮개 4, 바퀴 덮개 2, 아크릴 14</t>
         </is>
       </c>
       <c r="I21" s="32" t="inlineStr">
@@ -1358,7 +1356,7 @@
       </c>
       <c r="J21" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>모두 자가탭 · 아크릴에는 M3 와셔</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1366,16 @@
       </c>
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>M3 볼트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>M3×12</t>
+          <t>M3×16</t>
         </is>
       </c>
       <c r="D22" s="31" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
@@ -1391,7 +1389,7 @@
       </c>
       <c r="H22" s="32" t="inlineStr">
         <is>
-          <t>칼라 7, 디텐트 3, 클러치 덮개 7, 축 끝 덮개 4, 바퀴 덮개 2, 아크릴 14</t>
+          <t>바퀴 덮개 아래 받침</t>
         </is>
       </c>
       <c r="I22" s="32" t="inlineStr">
@@ -1401,7 +1399,7 @@
       </c>
       <c r="J22" s="32" t="inlineStr">
         <is>
-          <t>모두 자가탭 · 아크릴에는 M3 와셔</t>
+          <t>단가 미확인</t>
         </is>
       </c>
     </row>
@@ -1411,20 +1409,20 @@
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>M3 볼트</t>
+          <t>M3 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>M3×16</t>
+          <t>M3×20</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F23" s="33" t="n"/>
@@ -1434,7 +1432,7 @@
       </c>
       <c r="H23" s="32" t="inlineStr">
         <is>
-          <t>바퀴 덮개 아래 받침</t>
+          <t>슬리브 결합 (머리·너트는 육각 자리 안에 숨음)</t>
         </is>
       </c>
       <c r="I23" s="32" t="inlineStr">
@@ -1444,7 +1442,7 @@
       </c>
       <c r="J23" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>냄비머리(Ø6)는 육각 자리(맞변 5.7)에 안 들어감</t>
         </is>
       </c>
     </row>
@@ -1454,16 +1452,16 @@
       </c>
       <c r="B24" s="32" t="inlineStr">
         <is>
-          <t>M3 볼트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>M3×50</t>
+          <t>M3×25</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
@@ -1477,7 +1475,7 @@
       </c>
       <c r="H24" s="32" t="inlineStr">
         <is>
-          <t>끝 채움판 → 끝판</t>
+          <t>러그 (자가탭, 끝이 레일을 누름)</t>
         </is>
       </c>
       <c r="I24" s="32" t="inlineStr">
@@ -1487,7 +1485,7 @@
       </c>
       <c r="J24" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>M3×30 은 머리가 러그 위로 5mm 나와 캐리어에 닿음</t>
         </is>
       </c>
     </row>
@@ -1497,16 +1495,16 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>M3 볼트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>M3×8 6개 + M3×10 1개</t>
+          <t>M3×50</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
@@ -1520,7 +1518,7 @@
       </c>
       <c r="H25" s="32" t="inlineStr">
         <is>
-          <t>포크 카트리지 뚜껑 6, 클러치 포크 속선 누름 1</t>
+          <t>끝 채움판 → 끝판</t>
         </is>
       </c>
       <c r="I25" s="32" t="inlineStr">
@@ -1588,11 +1586,11 @@
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>M3 (바깥지름 7 내외)</t>
+          <t>M3 (바깥지름 7)</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
@@ -1606,7 +1604,7 @@
       </c>
       <c r="H27" s="32" t="inlineStr">
         <is>
-          <t>아크릴 고정 나사 밑 (아크릴 균열 방지)</t>
+          <t>아크릴 고정 나사 밑 14 (균열 방지) + 속선 누름 1</t>
         </is>
       </c>
       <c r="I27" s="32" t="inlineStr">
@@ -1616,7 +1614,7 @@
       </c>
       <c r="J27" s="32" t="inlineStr">
         <is>
-          <t>볼트너트 세트에 있으면 생략</t>
+          <t>단가 미확인</t>
         </is>
       </c>
     </row>
@@ -1626,16 +1624,16 @@
       </c>
       <c r="B28" s="32" t="inlineStr">
         <is>
-          <t>M4 볼트 + 너트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C28" s="31" t="inlineStr">
         <is>
-          <t>M4×30</t>
+          <t>M4×16</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="inlineStr">
         <is>
@@ -1649,7 +1647,7 @@
       </c>
       <c r="H28" s="32" t="inlineStr">
         <is>
-          <t>케이지 4, 피벗 8, 게이트 4, 받침 브래킷 4</t>
+          <t>클러치 포크 브래킷 (너트는 끝판 A 안쪽 홈)</t>
         </is>
       </c>
       <c r="I28" s="32" t="inlineStr">
@@ -1669,16 +1667,16 @@
       </c>
       <c r="B29" s="32" t="inlineStr">
         <is>
-          <t>M4 볼트 + 너트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>M4×16</t>
+          <t>M4×25</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
@@ -1692,7 +1690,7 @@
       </c>
       <c r="H29" s="32" t="inlineStr">
         <is>
-          <t>클러치 포크 브래킷 4, 페달 발판 4</t>
+          <t>페달 발판 (너트는 팔 앞면 홈)</t>
         </is>
       </c>
       <c r="I29" s="32" t="inlineStr">
@@ -1712,16 +1710,16 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>M4 볼트 + 너트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>M4×60</t>
+          <t>M4×30</t>
         </is>
       </c>
       <c r="D30" s="31" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E30" s="32" t="inlineStr">
         <is>
@@ -1735,7 +1733,7 @@
       </c>
       <c r="H30" s="32" t="inlineStr">
         <is>
-          <t>클러치 기둥</t>
+          <t>케이지 4, 피벗 8, 게이트 4, 받침 브래킷 4</t>
         </is>
       </c>
       <c r="I30" s="32" t="inlineStr">
@@ -1755,12 +1753,12 @@
       </c>
       <c r="B31" s="32" t="inlineStr">
         <is>
-          <t>M5 볼트 + 너트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>M5×10</t>
+          <t>M4×60</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
@@ -1778,7 +1776,7 @@
       </c>
       <c r="H31" s="32" t="inlineStr">
         <is>
-          <t>클러치 조절나사 (끝까지 조임 = 설정)</t>
+          <t>클러치 기둥</t>
         </is>
       </c>
       <c r="I31" s="32" t="inlineStr">
@@ -1788,7 +1786,7 @@
       </c>
       <c r="J31" s="32" t="inlineStr">
         <is>
-          <t>M5×12 이상 금지 (미끄럼 토크가 1.05N·m 까지 올라가 기어 설계 하중 초과)</t>
+          <t>단가 미확인</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1796,12 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>M5 볼트 + 너트</t>
+          <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C32" s="31" t="inlineStr">
         <is>
-          <t>M5×20</t>
+          <t>M5×10</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
@@ -1821,7 +1819,7 @@
       </c>
       <c r="H32" s="32" t="inlineStr">
         <is>
-          <t>클러치 릴리스 누름 볼트</t>
+          <t>클러치 조절나사 (끝까지 조임 = 설정)</t>
         </is>
       </c>
       <c r="I32" s="32" t="inlineStr">
@@ -1831,7 +1829,7 @@
       </c>
       <c r="J32" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>M5×12 이상 금지 (미끄럼 토크가 1.05N·m 까지 올라가 기어 설계 하중 초과)</t>
         </is>
       </c>
     </row>
@@ -1841,16 +1839,16 @@
       </c>
       <c r="B33" s="32" t="inlineStr">
         <is>
-          <t>M5 볼트 + 나일론 너트</t>
+          <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>M5×35</t>
+          <t>M5×20</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
@@ -1864,7 +1862,7 @@
       </c>
       <c r="H33" s="32" t="inlineStr">
         <is>
-          <t>클러치 포크 피벗</t>
+          <t>클러치 릴리스 누름 볼트</t>
         </is>
       </c>
       <c r="I33" s="32" t="inlineStr">
@@ -1884,12 +1882,12 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>M6 볼트·너트</t>
+          <t>M5 렌치볼트 + 평와셔</t>
         </is>
       </c>
       <c r="C34" s="31" t="inlineStr">
         <is>
-          <t>M6×50 10개 + 너트 10개</t>
+          <t>M5×8 3개 + M5×12 3개 + M5 와셔 3개</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
@@ -1900,26 +1898,24 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F34" s="33" t="n">
-        <v>4500</v>
-      </c>
+      <c r="F34" s="33" t="n"/>
       <c r="G34" s="34">
         <f>D34*F34</f>
         <v/>
       </c>
       <c r="H34" s="32" t="inlineStr">
         <is>
-          <t>페달 힌지 2 (남는 너트 4개는 모터 받침에 씀)</t>
+          <t>클러치 미끄럼 토크 조정 (설계서 8장 시험 3: 크면 M5×8, 작으면 M5×12 + 와셔 1장)</t>
         </is>
       </c>
       <c r="I34" s="32" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="J34" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /9679379731</t>
+          <t>시험 3 이 합격이면 안 씀 · 다시 주문하지 않으려면 같이 구매</t>
         </is>
       </c>
     </row>
@@ -1929,20 +1925,20 @@
       </c>
       <c r="B35" s="32" t="inlineStr">
         <is>
-          <t>M6 볼트</t>
+          <t>M5 렌치볼트 + 나일론 너트</t>
         </is>
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>M6×25</t>
+          <t>M5×70</t>
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F35" s="33" t="n"/>
@@ -1952,7 +1948,7 @@
       </c>
       <c r="H35" s="32" t="inlineStr">
         <is>
-          <t>모터 받침: K9B 브래킷 바닥 → 45 받침대 밑면 너트</t>
+          <t>클러치 포크 피벗 (팔·볼·보스 관통)</t>
         </is>
       </c>
       <c r="I35" s="32" t="inlineStr">
@@ -1962,7 +1958,7 @@
       </c>
       <c r="J35" s="32" t="inlineStr">
         <is>
-          <t>M6×30 이상 금지 (MDF 에 닿음) · 단가 미확인</t>
+          <t>너트는 손으로 닿을 때까지만 (세게 조이면 포크가 안 돎) · 단가 미확인</t>
         </is>
       </c>
     </row>
@@ -1972,16 +1968,16 @@
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>목재 나사</t>
+          <t>M6 렌치볼트</t>
         </is>
       </c>
       <c r="C36" s="31" t="inlineStr">
         <is>
-          <t>4×16</t>
+          <t>M6×25</t>
         </is>
       </c>
       <c r="D36" s="31" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
@@ -1995,7 +1991,7 @@
       </c>
       <c r="H36" s="32" t="inlineStr">
         <is>
-          <t>받침 브래킷 8, 클러치 덮개 4, 모터 받침 4, 페달 받침 8</t>
+          <t>모터 받침 4 (45 밑면 너트), 페달 피벗 2</t>
         </is>
       </c>
       <c r="I36" s="32" t="inlineStr">
@@ -2005,7 +2001,7 @@
       </c>
       <c r="J36" s="32" t="inlineStr">
         <is>
-          <t>MDF 12T 에 10~11 박힘 · 4×20 이상은 밑으로 나옴 · 단가 미확인</t>
+          <t>M6×30 이상 금지 (모터 받침: MDF 에 닿음, 페달: 가변저항 축에 닿음) · 단가 미확인</t>
         </is>
       </c>
     </row>
@@ -2015,16 +2011,16 @@
       </c>
       <c r="B37" s="32" t="inlineStr">
         <is>
-          <t>에폭시 접착제</t>
+          <t>M6 너트</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>2액형</t>
+          <t>M6 (맞변 10)</t>
         </is>
       </c>
       <c r="D37" s="31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
@@ -2038,7 +2034,7 @@
       </c>
       <c r="H37" s="32" t="inlineStr">
         <is>
-          <t>레버봉-핑거·손잡이, 아이들러 축, 클러치 와셔-허브, 고무 쿠션</t>
+          <t>모터 받침 (45 밑면 홈)</t>
         </is>
       </c>
       <c r="I37" s="32" t="inlineStr">
@@ -2058,16 +2054,16 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>순간접착제</t>
+          <t>M6 나일론 너트</t>
         </is>
       </c>
       <c r="C38" s="31" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>M6 (DIN985, 두께 6)</t>
         </is>
       </c>
       <c r="D38" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="32" t="inlineStr">
         <is>
@@ -2081,7 +2077,7 @@
       </c>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>덮개 스위치, 홀센서, 자석</t>
+          <t>페달 피벗 (팔 너트 홈, 볼트가 팔과 같이 돎 → 풀리지 않음)</t>
         </is>
       </c>
       <c r="I38" s="32" t="inlineStr">
@@ -2091,7 +2087,7 @@
       </c>
       <c r="J38" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>단가 미확인</t>
         </is>
       </c>
     </row>
@@ -2101,20 +2097,20 @@
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트</t>
+          <t>목재 나사</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>속선 + 아우터(바깥지름 5 내외)</t>
+          <t>4×16</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F39" s="33" t="n"/>
@@ -2124,7 +2120,7 @@
       </c>
       <c r="H39" s="32" t="inlineStr">
         <is>
-          <t>클러치 페달 → 클러치 포크</t>
+          <t>받침 브래킷 8, 클러치 덮개 4, 모터 받침 4, 페달 받침 8</t>
         </is>
       </c>
       <c r="I39" s="32" t="inlineStr">
@@ -2134,7 +2130,7 @@
       </c>
       <c r="J39" s="32" t="inlineStr">
         <is>
-          <t>아우터가 끝판 B 구멍 Ø6 에 들어가야 함</t>
+          <t>MDF 12T 에 10~11 박힘 · 4×20 이상은 밑으로 나옴 · 단가 미확인</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2140,12 @@
       </c>
       <c r="B40" s="32" t="inlineStr">
         <is>
-          <t>인장 스프링</t>
+          <t>에폭시 접착제</t>
         </is>
       </c>
       <c r="C40" s="31" t="inlineStr">
         <is>
-          <t>선경 1.0 외경 7, 1m</t>
+          <t>2액형</t>
         </is>
       </c>
       <c r="D40" s="31" t="n">
@@ -2160,16 +2156,14 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F40" s="33" t="n">
-        <v>8000</v>
-      </c>
+      <c r="F40" s="33" t="n"/>
       <c r="G40" s="34">
         <f>D40*F40</f>
         <v/>
       </c>
       <c r="H40" s="32" t="inlineStr">
         <is>
-          <t>페달 복귀 (잘라 고리 만듦)</t>
+          <t>레버봉-핑거·손잡이, 아이들러 축, 클러치 와셔-허브, 고무 쿠션, 페달 가변저항 2</t>
         </is>
       </c>
       <c r="I40" s="32" t="inlineStr">
@@ -2179,7 +2173,7 @@
       </c>
       <c r="J40" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /7939346368</t>
+          <t>단가 미확인</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2183,12 @@
       </c>
       <c r="B41" s="32" t="inlineStr">
         <is>
-          <t>MDF 판</t>
+          <t>순간접착제</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>12T 300×1200 재단</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D41" s="31" t="n">
@@ -2202,19 +2196,17 @@
       </c>
       <c r="E41" s="32" t="inlineStr">
         <is>
-          <t>장</t>
-        </is>
-      </c>
-      <c r="F41" s="33" t="n">
-        <v>9600</v>
-      </c>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="n"/>
       <c r="G41" s="34">
         <f>D41*F41</f>
         <v/>
       </c>
       <c r="H41" s="32" t="inlineStr">
         <is>
-          <t>바닥판 750×300 (모터·클러치 덮개 포함)</t>
+          <t>덮개 스위치, 홀센서, 자석</t>
         </is>
       </c>
       <c r="I41" s="32" t="inlineStr">
@@ -2224,7 +2216,7 @@
       </c>
       <c r="J41" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /71452005</t>
+          <t>보유하면 생략</t>
         </is>
       </c>
     </row>
@@ -2234,32 +2226,30 @@
       </c>
       <c r="B42" s="32" t="inlineStr">
         <is>
-          <t>투명 아크릴</t>
+          <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
       <c r="C42" s="31" t="inlineStr">
         <is>
-          <t>A3 3T</t>
+          <t>속선(니플 달린 것) 2m + 아우터 바깥지름 5 2m + 끝 캡</t>
         </is>
       </c>
       <c r="D42" s="31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>장</t>
-        </is>
-      </c>
-      <c r="F42" s="33" t="n">
-        <v>9000</v>
-      </c>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="n"/>
       <c r="G42" s="34">
         <f>D42*F42</f>
         <v/>
       </c>
       <c r="H42" s="32" t="inlineStr">
         <is>
-          <t>덮개 윗판 250×321, 옆판 200×321 × 2</t>
+          <t>클러치 페달 → 클러치 포크</t>
         </is>
       </c>
       <c r="I42" s="32" t="inlineStr">
@@ -2269,7 +2259,7 @@
       </c>
       <c r="J42" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /9593337115 · 재단 주문 가능하면 치수대로</t>
+          <t>아우터가 끝판 B 구멍 Ø6·페달 받침 Ø5.6 에 들어가야 함 · 니플은 페달 팔 Ø3.4 구멍보다 커야 함</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2269,12 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + 케이블</t>
+          <t>MDF 판</t>
         </is>
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>ATmega32u4</t>
+          <t>12T 300×1200 재단</t>
         </is>
       </c>
       <c r="D43" s="31" t="n">
@@ -2292,11 +2282,11 @@
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F43" s="33" t="n">
-        <v>9200</v>
+        <v>9600</v>
       </c>
       <c r="G43" s="34">
         <f>D43*F43</f>
@@ -2304,7 +2294,7 @@
       </c>
       <c r="H43" s="32" t="inlineStr">
         <is>
-          <t>센서 → PC 게임 입력 + 모터 허가 출력</t>
+          <t>바닥판 750×300 (모터·클러치 덮개 포함) + 남는 450×300 = 페달 받침판 (바닥)</t>
         </is>
       </c>
       <c r="I43" s="32" t="inlineStr">
@@ -2314,7 +2304,7 @@
       </c>
       <c r="J43" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /1119152790</t>
+          <t>v3 단가 · 쿠팡 /71452005</t>
         </is>
       </c>
     </row>
@@ -2324,24 +2314,24 @@
       </c>
       <c r="B44" s="32" t="inlineStr">
         <is>
-          <t>홀센서 A3144</t>
+          <t>투명 아크릴</t>
         </is>
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>3핀 소자</t>
+          <t>A3 3T</t>
         </is>
       </c>
       <c r="D44" s="31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F44" s="33" t="n">
-        <v>90</v>
+        <v>9000</v>
       </c>
       <c r="G44" s="34">
         <f>D44*F44</f>
@@ -2349,7 +2339,7 @@
       </c>
       <c r="H44" s="32" t="inlineStr">
         <is>
-          <t>기어 위치 6 + 출력 rpm 1</t>
+          <t>덮개 윗판 250×321, 옆판 200×321 × 2</t>
         </is>
       </c>
       <c r="I44" s="32" t="inlineStr">
@@ -2359,7 +2349,7 @@
       </c>
       <c r="J44" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /8520223332</t>
+          <t>v3 단가 · 쿠팡 /9593337115 · 재단 주문 가능하면 치수대로</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2359,12 @@
       </c>
       <c r="B45" s="32" t="inlineStr">
         <is>
-          <t>네오디뮴 자석</t>
+          <t>아두이노 레오나르도 R3 + 케이블</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Ø6×3mm 40개</t>
+          <t>ATmega32u4</t>
         </is>
       </c>
       <c r="D45" s="31" t="n">
@@ -2382,11 +2372,11 @@
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F45" s="33" t="n">
-        <v>11300</v>
+        <v>9200</v>
       </c>
       <c r="G45" s="34">
         <f>D45*F45</f>
@@ -2394,7 +2384,7 @@
       </c>
       <c r="H45" s="32" t="inlineStr">
         <is>
-          <t>러그 3 + 표시 바퀴 4</t>
+          <t>센서 → PC 게임 입력 + 모터 허가 출력</t>
         </is>
       </c>
       <c r="I45" s="32" t="inlineStr">
@@ -2404,7 +2394,7 @@
       </c>
       <c r="J45" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /7119515778</t>
+          <t>v3 단가 · 쿠팡 /1119152790</t>
         </is>
       </c>
     </row>
@@ -2414,16 +2404,16 @@
       </c>
       <c r="B46" s="32" t="inlineStr">
         <is>
-          <t>가변저항 B10K</t>
+          <t>홀센서 A3144</t>
         </is>
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>노브 포함</t>
+          <t>3핀 소자</t>
         </is>
       </c>
       <c r="D46" s="31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
@@ -2431,7 +2421,7 @@
         </is>
       </c>
       <c r="F46" s="33" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="G46" s="34">
         <f>D46*F46</f>
@@ -2439,7 +2429,7 @@
       </c>
       <c r="H46" s="32" t="inlineStr">
         <is>
-          <t>핸들·클러치·브레이크</t>
+          <t>기어 위치 6 + 출력 rpm 1</t>
         </is>
       </c>
       <c r="I46" s="32" t="inlineStr">
@@ -2449,7 +2439,7 @@
       </c>
       <c r="J46" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 축 지름·반달 치수 미확인 (페달 팔 구멍 Ø6.1, 평면 4.6)</t>
+          <t>v3 단가 · 쿠팡 /8520223332</t>
         </is>
       </c>
     </row>
@@ -2459,24 +2449,24 @@
       </c>
       <c r="B47" s="32" t="inlineStr">
         <is>
-          <t>마이크로스위치</t>
+          <t>네오디뮴 자석</t>
         </is>
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>KW-11-3Z 레버형</t>
+          <t>Ø6×3mm 40개</t>
         </is>
       </c>
       <c r="D47" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>봉</t>
         </is>
       </c>
       <c r="F47" s="33" t="n">
-        <v>400</v>
+        <v>11300</v>
       </c>
       <c r="G47" s="34">
         <f>D47*F47</f>
@@ -2484,7 +2474,7 @@
       </c>
       <c r="H47" s="32" t="inlineStr">
         <is>
-          <t>덮개 열림 감지 1 + 여분 1</t>
+          <t>러그 3 + 표시 바퀴 4</t>
         </is>
       </c>
       <c r="I47" s="32" t="inlineStr">
@@ -2494,7 +2484,7 @@
       </c>
       <c r="J47" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /9167678186</t>
+          <t>v3 단가 · 쿠팡 /7119515778</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2494,30 @@
       </c>
       <c r="B48" s="32" t="inlineStr">
         <is>
-          <t>점퍼 케이블</t>
+          <t>가변저항 B10K</t>
         </is>
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>M-F 40P 40cm</t>
+          <t>회전형 16mm, 축 Ø6 반달(D컷, 평면까지 4.5~4.6), 축 길이 15mm(장착면부터), 부싱 M7</t>
         </is>
       </c>
       <c r="D48" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="32" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F48" s="33" t="n">
-        <v>5300</v>
-      </c>
+      <c r="F48" s="33" t="n"/>
       <c r="G48" s="34">
         <f>D48*F48</f>
         <v/>
       </c>
       <c r="H48" s="32" t="inlineStr">
         <is>
-          <t>센서 배선</t>
+          <t>클러치·브레이크 페달 2 + 핸들 1</t>
         </is>
       </c>
       <c r="I48" s="32" t="inlineStr">
@@ -2539,7 +2527,7 @@
       </c>
       <c r="J48" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /9699042565</t>
+          <t>축이 톱니(널링)형이거나 20mm 면 페달에 안 맞음 · 핸들에 센서가 이미 있으면 2개 · 도착 후 실측해서 페달 출력</t>
         </is>
       </c>
     </row>
@@ -2549,24 +2537,24 @@
       </c>
       <c r="B49" s="32" t="inlineStr">
         <is>
-          <t>만능기판</t>
+          <t>마이크로스위치</t>
         </is>
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>20개 묶음</t>
+          <t>KW-11-3Z 레버형</t>
         </is>
       </c>
       <c r="D49" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="32" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F49" s="33" t="n">
-        <v>15000</v>
+        <v>400</v>
       </c>
       <c r="G49" s="34">
         <f>D49*F49</f>
@@ -2574,7 +2562,7 @@
       </c>
       <c r="H49" s="32" t="inlineStr">
         <is>
-          <t>센서 배선</t>
+          <t>덮개 열림 감지 1 + 여분 1</t>
         </is>
       </c>
       <c r="I49" s="32" t="inlineStr">
@@ -2584,7 +2572,7 @@
       </c>
       <c r="J49" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /9661304796</t>
+          <t>v3 단가 · 쿠팡 /9167678186</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2582,12 @@
       </c>
       <c r="B50" s="32" t="inlineStr">
         <is>
-          <t>자동차 릴레이 + 소켓</t>
+          <t>점퍼 케이블</t>
         </is>
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>12V, 접점 40A, 4핀</t>
+          <t>M-F 40P 40cm</t>
         </is>
       </c>
       <c r="D50" s="31" t="n">
@@ -2610,14 +2598,16 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F50" s="33" t="n"/>
+      <c r="F50" s="33" t="n">
+        <v>5300</v>
+      </c>
       <c r="G50" s="34">
         <f>D50*F50</f>
         <v/>
       </c>
       <c r="H50" s="32" t="inlineStr">
         <is>
-          <t>모터 전원 주 스위치</t>
+          <t>센서 배선</t>
         </is>
       </c>
       <c r="I50" s="32" t="inlineStr">
@@ -2627,7 +2617,7 @@
       </c>
       <c r="J50" s="32" t="inlineStr">
         <is>
-          <t>검색어 "12V 40A 릴레이 소켓" · 코일 회로에 비상정지·덮개 스위치·5V 릴레이 모듈 직렬</t>
+          <t>v3 단가 · 쿠팡 /9699042565</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2627,12 @@
       </c>
       <c r="B51" s="32" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더</t>
+          <t>만능기판</t>
         </is>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>15A</t>
+          <t>20개 묶음</t>
         </is>
       </c>
       <c r="D51" s="31" t="n">
@@ -2650,17 +2640,19 @@
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F51" s="33" t="n"/>
+          <t>봉</t>
+        </is>
+      </c>
+      <c r="F51" s="33" t="n">
+        <v>15000</v>
+      </c>
       <c r="G51" s="34">
         <f>D51*F51</f>
         <v/>
       </c>
       <c r="H51" s="32" t="inlineStr">
         <is>
-          <t>배터리 + 단자 바로 옆</t>
+          <t>센서 배선</t>
         </is>
       </c>
       <c r="I51" s="32" t="inlineStr">
@@ -2670,7 +2662,7 @@
       </c>
       <c r="J51" s="32" t="inlineStr">
         <is>
-          <t>여분 퓨즈 2개 권장</t>
+          <t>v3 단가 · 쿠팡 /9661304796</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2672,12 @@
       </c>
       <c r="B52" s="32" t="inlineStr">
         <is>
-          <t>비상정지 스위치</t>
+          <t>자동차 릴레이 + 소켓</t>
         </is>
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>버섯형, b접점(NC)</t>
+          <t>12V, 접점 40A, 4핀</t>
         </is>
       </c>
       <c r="D52" s="31" t="n">
@@ -2703,7 +2695,7 @@
       </c>
       <c r="H52" s="32" t="inlineStr">
         <is>
-          <t>운영자 비상 차단 (릴레이 코일 회로)</t>
+          <t>모터 전원 주 스위치</t>
         </is>
       </c>
       <c r="I52" s="32" t="inlineStr">
@@ -2713,7 +2705,7 @@
       </c>
       <c r="J52" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>검색어 "12V 40A 릴레이 소켓" · 코일 회로에 비상정지·덮개 스위치·5V 릴레이 모듈 직렬</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2715,12 @@
       </c>
       <c r="B53" s="32" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈</t>
+          <t>블레이드 퓨즈 + 인라인 홀더</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>1채널</t>
+          <t>15A</t>
         </is>
       </c>
       <c r="D53" s="31" t="n">
@@ -2736,7 +2728,7 @@
       </c>
       <c r="E53" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F53" s="33" t="n"/>
@@ -2746,7 +2738,7 @@
       </c>
       <c r="H53" s="32" t="inlineStr">
         <is>
-          <t>아두이노 워치독 → 주 릴레이 코일 차단</t>
+          <t>배터리 + 단자 바로 옆</t>
         </is>
       </c>
       <c r="I53" s="32" t="inlineStr">
@@ -2756,7 +2748,7 @@
       </c>
       <c r="J53" s="32" t="inlineStr">
         <is>
-          <t>로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
+          <t>여분 퓨즈 2개 권장</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2758,16 @@
       </c>
       <c r="B54" s="32" t="inlineStr">
         <is>
-          <t>다이오드 1N4007</t>
-        </is>
-      </c>
-      <c r="C54" s="31" t="inlineStr"/>
+          <t>비상정지 스위치</t>
+        </is>
+      </c>
+      <c r="C54" s="31" t="inlineStr">
+        <is>
+          <t>버섯형, b접점(NC)</t>
+        </is>
+      </c>
       <c r="D54" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="32" t="inlineStr">
         <is>
@@ -2785,7 +2781,7 @@
       </c>
       <c r="H54" s="32" t="inlineStr">
         <is>
-          <t>주 릴레이 코일 역기전력 흡수 1 + 여분 1</t>
+          <t>운영자 비상 차단 (릴레이 코일 회로)</t>
         </is>
       </c>
       <c r="I54" s="32" t="inlineStr">
@@ -2795,7 +2791,7 @@
       </c>
       <c r="J54" s="32" t="inlineStr">
         <is>
-          <t>내장 다이오드 릴레이면 생략</t>
+          <t>단가 미확인</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2801,12 @@
       </c>
       <c r="B55" s="32" t="inlineStr">
         <is>
-          <t>전선</t>
+          <t>5V 릴레이 모듈</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>1.5mm² 이상, 적·흑 각 2m</t>
+          <t>1채널</t>
         </is>
       </c>
       <c r="D55" s="31" t="n">
@@ -2818,7 +2814,7 @@
       </c>
       <c r="E55" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F55" s="33" t="n"/>
@@ -2828,7 +2824,7 @@
       </c>
       <c r="H55" s="32" t="inlineStr">
         <is>
-          <t>배터리-퓨즈-릴레이-모터 드라이버</t>
+          <t>아두이노 워치독 → 주 릴레이 코일 차단</t>
         </is>
       </c>
       <c r="I55" s="32" t="inlineStr">
@@ -2838,7 +2834,7 @@
       </c>
       <c r="J55" s="32" t="inlineStr">
         <is>
-          <t>퓨즈 15A 기준</t>
+          <t>로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
         </is>
       </c>
     </row>
@@ -2848,20 +2844,16 @@
       </c>
       <c r="B56" s="32" t="inlineStr">
         <is>
-          <t>압착 단자 세트</t>
-        </is>
-      </c>
-      <c r="C56" s="31" t="inlineStr">
-        <is>
-          <t>250 규격(6.3mm) 절연 암 평형 단자 + 수축 튜브</t>
-        </is>
-      </c>
+          <t>다이오드 1N4007</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="inlineStr"/>
       <c r="D56" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F56" s="33" t="n"/>
@@ -2871,7 +2863,7 @@
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>퓨즈 홀더·릴레이 소켓 연결 (배터리 쪽은 키트 선 단자 재사용)</t>
+          <t>주 릴레이 코일 역기전력 흡수 1 + 여분 1</t>
         </is>
       </c>
       <c r="I56" s="32" t="inlineStr">
@@ -2881,7 +2873,7 @@
       </c>
       <c r="J56" s="32" t="inlineStr">
         <is>
-          <t>배터리 단자 = 6.3mm 평형 탭(사진 확인) · 홀더·소켓에 단자 포함이면 생략</t>
+          <t>내장 다이오드 릴레이면 생략</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2883,12 @@
       </c>
       <c r="B57" s="32" t="inlineStr">
         <is>
-          <t>저항</t>
+          <t>전선</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>10kΩ 1개 + 4.7kΩ 1개 (1/4W)</t>
+          <t>1.5mm² 이상, 적·흑 각 2m</t>
         </is>
       </c>
       <c r="D57" s="31" t="n">
@@ -2914,7 +2906,7 @@
       </c>
       <c r="H57" s="32" t="inlineStr">
         <is>
-          <t>안전 회로 감지 (비상정지·덮개 뒤 12V → 아두이노 A4)</t>
+          <t>배터리-퓨즈-릴레이-모터 드라이버</t>
         </is>
       </c>
       <c r="I57" s="32" t="inlineStr">
@@ -2924,7 +2916,7 @@
       </c>
       <c r="J57" s="32" t="inlineStr">
         <is>
-          <t>풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
+          <t>퓨즈 15A 기준</t>
         </is>
       </c>
     </row>
@@ -2934,20 +2926,20 @@
       </c>
       <c r="B58" s="32" t="inlineStr">
         <is>
-          <t>PLA 필라멘트</t>
+          <t>압착 단자 세트</t>
         </is>
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>2.85mm, 1kg 롤</t>
+          <t>250 규격(6.3mm) 절연 암 평형 단자 + 수축 튜브</t>
         </is>
       </c>
       <c r="D58" s="31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F58" s="33" t="n"/>
@@ -2957,7 +2949,7 @@
       </c>
       <c r="H58" s="32" t="inlineStr">
         <is>
-          <t>출력 예상 4.03kg + 실패 여유 15% − 보유 750g 롤 1개</t>
+          <t>퓨즈 홀더·릴레이 소켓 연결 (배터리 쪽은 키트 선 단자 재사용)</t>
         </is>
       </c>
       <c r="I58" s="32" t="inlineStr">
@@ -2967,7 +2959,7 @@
       </c>
       <c r="J58" s="32" t="inlineStr">
         <is>
-          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 단가 미확인</t>
+          <t>배터리 단자 = 6.3mm 평형 탭(사진 확인) · 홀더·소켓에 단자 포함이면 생략</t>
         </is>
       </c>
     </row>
@@ -2977,12 +2969,12 @@
       </c>
       <c r="B59" s="32" t="inlineStr">
         <is>
-          <t>걸이 저울</t>
+          <t>저항</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>0~5kg, 10g 단위</t>
+          <t>10kΩ 1개 + 4.7kΩ 1개 (1/4W)</t>
         </is>
       </c>
       <c r="D59" s="31" t="n">
@@ -2990,7 +2982,7 @@
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F59" s="33" t="n"/>
@@ -3000,17 +2992,17 @@
       </c>
       <c r="H59" s="32" t="inlineStr">
         <is>
-          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
+          <t>안전 회로 감지 (비상정지·덮개 뒤 12V → 아두이노 A4)</t>
         </is>
       </c>
       <c r="I59" s="32" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="J59" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
         </is>
       </c>
     </row>
@@ -3020,20 +3012,20 @@
       </c>
       <c r="B60" s="32" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스</t>
+          <t>PLA 필라멘트</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>0.01mm 표시, 150mm</t>
+          <t>2.85mm, 1kg 롤</t>
         </is>
       </c>
       <c r="D60" s="31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>롤</t>
         </is>
       </c>
       <c r="F60" s="33" t="n"/>
@@ -3043,7 +3035,7 @@
       </c>
       <c r="H60" s="32" t="inlineStr">
         <is>
-          <t>쿠폰·핀 구멍·축 지름 확인</t>
+          <t>출력 예상 4.05kg + 실패 여유 15% − 보유 750g 롤 1개</t>
         </is>
       </c>
       <c r="I60" s="32" t="inlineStr">
@@ -3053,7 +3045,7 @@
       </c>
       <c r="J60" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 단가 미확인</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3055,12 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>배송비</t>
+          <t>육각 렌치 세트</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>새 판매처 포함</t>
+          <t>2.5·3·4·5mm 포함</t>
         </is>
       </c>
       <c r="D61" s="31" t="n">
@@ -3076,7 +3068,7 @@
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>식</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F61" s="33" t="n"/>
@@ -3084,48 +3076,259 @@
         <f>D61*F61</f>
         <v/>
       </c>
-      <c r="H61" s="32" t="n"/>
+      <c r="H61" s="32" t="inlineStr">
+        <is>
+          <t>렌치볼트 M3~M6, 무두볼트</t>
+        </is>
+      </c>
       <c r="I61" s="32" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="J61" s="32" t="inlineStr">
         <is>
+          <t>보유하면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="29.25" customHeight="1" s="16">
+      <c r="A62" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>드릴 날</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>Ø3.4 (전동 드릴용)</t>
+        </is>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F62" s="33" t="n"/>
+      <c r="G62" s="34">
+        <f>D62*F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>아크릴 나사 구멍 14 (설계서 5장 위치)</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>드릴이 없으면 재단 업체에 구멍까지 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="29.25" customHeight="1" s="16">
+      <c r="A63" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>납땜 인두 + 실납</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr"/>
+      <c r="D63" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="32" t="inlineStr">
+        <is>
+          <t>세트</t>
+        </is>
+      </c>
+      <c r="F63" s="33" t="n"/>
+      <c r="G63" s="34">
+        <f>D63*F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="32" t="inlineStr">
+        <is>
+          <t>만능기판 (분압 저항·다이오드·배선)</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="J63" s="32" t="inlineStr">
+        <is>
+          <t>보유하면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="29.25" customHeight="1" s="16">
+      <c r="A64" s="31" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="32" t="inlineStr">
+        <is>
+          <t>걸이 저울</t>
+        </is>
+      </c>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>0~5kg, 10g 단위</t>
+        </is>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F64" s="33" t="n"/>
+      <c r="G64" s="34">
+        <f>D64*F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="J64" s="32" t="inlineStr">
+        <is>
+          <t>보유하면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="29.25" customHeight="1" s="16">
+      <c r="A65" s="31" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>디지털 캘리퍼스</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>0.01mm 표시, 150mm</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F65" s="33" t="n"/>
+      <c r="G65" s="34">
+        <f>D65*F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="32" t="inlineStr">
+        <is>
+          <t>쿠폰·핀 구멍·축 지름 확인</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J65" s="32" t="inlineStr">
+        <is>
+          <t>보유하면 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="29.25" customHeight="1" s="16">
+      <c r="A66" s="31" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>배송비</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>새 판매처 포함</t>
+        </is>
+      </c>
+      <c r="D66" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="F66" s="33" t="n"/>
+      <c r="G66" s="34">
+        <f>D66*F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="32" t="n"/>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J66" s="32" t="inlineStr">
+        <is>
           <t>v3 는 22,900원 · 새 항목 판매처에 따라 달라짐 (미확인)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="38" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>합계 (확정 항목, 단가 입력된 것만)</t>
         </is>
       </c>
-      <c r="G62" s="39">
-        <f>SUMIFS(G5:G61,I5:I61,"확정")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="38" t="inlineStr">
+      <c r="G67" s="39">
+        <f>SUMIFS(G5:G66,I5:I66,"확정")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t>합계 (선택 포함)</t>
         </is>
       </c>
-      <c r="G63" s="39">
-        <f>SUM(G5:G61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="38" t="inlineStr">
+      <c r="G68" s="39">
+        <f>SUM(G5:G66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="38" t="inlineStr">
         <is>
           <t>단가 미확인 항목 수</t>
         </is>
       </c>
-      <c r="G64" s="40">
-        <f>COUNTBLANK(F5:F61)</f>
+      <c r="G69" s="40">
+        <f>COUNTBLANK(F5:F66)</f>
         <v/>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="J7" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 소망트레이딩 · 절단·양면 D컷 비용 미확인(전화 문의)</t>
+          <t>v3 단가 · 소망트레이딩(smball.co.kr) · 절단·양면 D컷 가능 여부·비용 미확인 → 불가하면 미스미 양면 D컷 샤프트(길이 지정)</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="J48" s="32" t="inlineStr">
         <is>
-          <t>축이 톱니(널링)형이거나 20mm 면 페달에 안 맞음 · 핸들에 센서가 이미 있으면 2개 · 도착 후 실측해서 페달 출력</t>
+          <t>축이 톱니(널링)형이거나 20mm 면 페달에 안 맞음 · 핸들은 센서 없음 확인(2026-10-20) → 3개 · 도착 후 실측해서 페달 출력</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>1.5mm² 이상, 적·흑 각 2m</t>
+          <t>1.5mm²(16AWG) 이상, 적·흑 각 2m</t>
         </is>
       </c>
       <c r="D57" s="31" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="J57" s="32" t="inlineStr">
         <is>
-          <t>퓨즈 15A 기준</t>
+          <t>키트 배터리 선 16AWG 확인(2026-10-20) → 퓨즈 15A 유지</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -563,7 +563,7 @@
     <row r="2" ht="15" customHeight="1" s="16">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다(비고의 검색어로 확인).</t>
+          <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다. 품명을 누르면 쿠팡 상품·검색으로 (스프링은 디바이스마트, 축은 소망트레이딩).</t>
         </is>
       </c>
     </row>
@@ -3333,6 +3333,69 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -1094,7 +1094,7 @@
       </c>
       <c r="J15" s="32" t="inlineStr">
         <is>
-          <t>디바이스마트 no=15336269 · 선경 미표기 → 스프링 상수·허용 하중으로 역산 선경 약 1.4~1.6, 안지름 약 14.8~15.2 (필요 12.5 이상, 미검증)</t>
+          <t>디바이스마트 no=15336269 · 8,360원 = 1개 값(VAT 포함, 2026-10-20 화면 확인) · 반품 불가 · 준비 4~5일 · 선경 미표기 → 스프링 상수·허용 하중으로 역산 선경 약 1.4~1.6, 안지름 약 14.8~15.2 (필요 12.5 이상, 미검증)</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -1094,7 +1094,7 @@
       </c>
       <c r="J15" s="32" t="inlineStr">
         <is>
-          <t>디바이스마트 no=15336269 · 8,360원 = 1개 값(VAT 포함, 2026-10-20 화면 확인) · 반품 불가 · 준비 4~5일 · 선경 미표기 → 스프링 상수·허용 하중으로 역산 선경 약 1.4~1.6, 안지름 약 14.8~15.2 (필요 12.5 이상, 미검증)</t>
+          <t>디바이스마트 no=15336269 · 8,360원 = 1개 값(VAT 포함, 2026-10-20 화면 확인) · 반품 불가 · 준비 4~5일 · 재질 SUS304, 하중 ±10%, 끝면 연삭 · 선경 미표기 → k·허용 길이로 역산 선경 1.7 이하, 안지름 14.6 이상 (필요 12.5, 실측 전)</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v3" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v2(9-25)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주문방법" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v2(9-25)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\-#,##0;\-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -103,6 +104,9 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -164,7 +168,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -285,6 +289,12 @@
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -563,7 +573,7 @@
     <row r="2" ht="15" customHeight="1" s="16">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다. 품명을 누르면 쿠팡 상품·검색으로 (스프링은 디바이스마트, 축은 소망트레이딩).</t>
+          <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다. 품명을 누르면 쿠팡 상품·검색으로 (스프링은 디바이스마트, 축은 소망트레이딩). 판매처별 주문 방법은 두 번째 시트 '주문방법'.</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1920,12 @@
       </c>
       <c r="I34" s="32" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="J34" s="32" t="inlineStr">
         <is>
-          <t>시험 3 이 합격이면 안 씀 · 다시 주문하지 않으려면 같이 구매</t>
+          <t>시험 3 이 합격이면 안 씀 · 다시 주문하지 않으려고 같이 구매</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3093,7 @@
       </c>
       <c r="I61" s="32" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="J61" s="32" t="inlineStr">
@@ -3126,12 +3136,12 @@
       </c>
       <c r="I62" s="32" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="J62" s="32" t="inlineStr">
         <is>
-          <t>드릴이 없으면 재단 업체에 구멍까지 주문</t>
+          <t>보유하면 생략 · 드릴이 없으면 아크릴 재단 업체에 구멍까지 주문</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3175,7 @@
       </c>
       <c r="I63" s="32" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="J63" s="32" t="inlineStr">
@@ -3208,7 +3218,7 @@
       </c>
       <c r="I64" s="32" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="J64" s="32" t="inlineStr">
@@ -3402,6 +3412,110 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="16" min="1" max="1"/>
+    <col width="34" customWidth="1" style="16" min="2" max="2"/>
+    <col width="110" customWidth="1" style="16" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="41" t="inlineStr">
+        <is>
+          <t>판매처</t>
+        </is>
+      </c>
+      <c r="B1" s="41" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C1" s="41" t="inlineStr">
+        <is>
+          <t>방법 · 확인할 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="B2" s="42" t="inlineStr">
+        <is>
+          <t>압축 스프링 C252 9개, C147 3개</t>
+        </is>
+      </c>
+      <c r="C2" s="42" t="inlineStr">
+        <is>
+          <t>한 장바구니로 주문. C252 = 1개 8,360원(VAT 포함), 수량 9 로 내려감 확인(2026-10-20), 반품·취소 불가, 준비 4~5일. C252: https://www.devicemart.co.kr/goods/view?no=15336269 / C147: https://www.devicemart.co.kr/goods/view?no=15336164 (외경 5, 자유장 10, P1 1.77N@6.47, P2 2.79N@4.41 인지 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="42" t="inlineStr">
+        <is>
+          <t>소망트레이딩 (smball.co.kr)</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="inlineStr">
+        <is>
+          <t>연마봉 Ø12 435·358(양면 D컷)·160·55, Ø6 371 ×3</t>
+        </is>
+      </c>
+      <c r="C3" s="42" t="inlineStr">
+        <is>
+          <t>게시판·카카오톡에 아래 문구 그대로: "열처리 연마봉 Ø12 를 아래처럼 절단·가공 가능한지, 가격이 얼마인지 문의드립니다. 1) 435mm 1개, 2) 358mm 1개: 두 개 모두 전체 길이 양면 D컷 (마주 보는 두 면, 면 사이 10.0mm, 한쪽 깊이 1.0mm) 3) 160mm 1개, 4) 55mm 1개: 가공 없음 5) Ø6 연마봉 371mm 3개: 가공 없음. 길이 오차 ±0.5mm 이내 가능한지도 알려 주세요." → D컷 불가면 435·358 만 미스미 양면 D컷 샤프트(길이 지정)로, 나머지는 소망트레이딩</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>위 두 곳을 뺀 나머지 전부</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>구매목록 시트의 품명을 누르면 쿠팡 상품·검색. 고를 때 규격 칸과 맞춰 볼 것: ① 가변저항 = 축 Ø6 반달(D컷) 15mm + 부싱 M7 (톱니 축·20mm 안 됨) ② 볼트 = 렌치볼트(육각 홈, 머리 Ø5.5) — 냄비머리 안 됨 ③ 샤프트 칼라 = 안지름 6, 바깥지름 12 이하 ④ 6003ZZ = 17×35×10 ⑤ 평행핀 = Ø5 정확히 (25·40 길이) ⑥ PLA = 2.85mm ⑦ 목재나사 = 4×16 (4×20 이상 안 됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>도착 후</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>① 가변저항 축 지름·평면·길이 실측 → 80·82 페달 출력 (다르면 수정) ② 핀·6003 도착 → 02 시험편 출력 ③ 00 쿠폰 구멍마다 안 들어감/꽉/헐거움 → 공차 확정 후 전체 출력 ④ C252 안지름 실측 (12.5 이상)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -4883,7 +4997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주문방법" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v2(9-25)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="구매목록_v4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="주문방법" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="구매목록_v3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="구매목록_v2(9-25)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -573,7 +573,7 @@
     <row r="2" ht="15" customHeight="1" s="16">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다. 품명을 누르면 쿠팡 상품·검색으로 (스프링은 디바이스마트, 축은 소망트레이딩). 판매처별 주문 방법은 두 번째 시트 '주문방법'.</t>
+          <t>작성일 2026-10-19 · 설계서 v4.1 기준 · 노란 칸(단가)만 입력하면 금액·합계가 계산됩니다. 단가는 v3 표(2026-10-19 확인)에서 가져온 것만 넣음, 비어 있는 칸은 미확인입니다. 나머지 단가는 2026-10-20 쿠팡 등에서 확인. 품명을 누르면 고른 상품으로 (스프링·가변저항은 디바이스마트, 축은 소망트레이딩). 판매처별 주문 방법은 두 번째 시트 '주문방법'.</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F6" s="33" t="n"/>
+      <c r="F6" s="33" t="n">
+        <v>1100</v>
+      </c>
       <c r="G6" s="34">
         <f>D6*F6</f>
         <v/>
@@ -713,7 +715,7 @@
       </c>
       <c r="J6" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인 · 검색어 "6003ZZ" · 02 시험편으로 압입 자리 확인</t>
+          <t>KYK 6003ZZ 1개 (표준 17×35×10) · 배송비 3,000 · 2026-10-20 확인 · 02 시험편으로 압입 자리 확인</t>
         </is>
       </c>
     </row>
@@ -784,7 +786,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F8" s="33" t="n"/>
+      <c r="F8" s="33" t="n">
+        <v>1600</v>
+      </c>
       <c r="G8" s="34">
         <f>D8*F8</f>
         <v/>
@@ -801,7 +805,7 @@
       </c>
       <c r="J8" s="32" t="inlineStr">
         <is>
-          <t>1m 에서 위 3개를 자르면 약 41mm 만 남아 따로 필요 · 단가 미확인</t>
+          <t>소망트레이딩 "열처리 연마봉 절단 판매" 12파이 100mm 옵션 1,600 (2026-10-20 확인) · 55 절단은 문의 문구대로 요청 (안 되면 100 받아서 자름)</t>
         </is>
       </c>
     </row>
@@ -827,7 +831,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F9" s="33" t="n"/>
+      <c r="F9" s="33" t="n">
+        <v>5200</v>
+      </c>
       <c r="G9" s="34">
         <f>D9*F9</f>
         <v/>
@@ -844,7 +850,7 @@
       </c>
       <c r="J9" s="32" t="inlineStr">
         <is>
-          <t>소망트레이딩 · 단가 미확인 (v3 참고: 200mm 2,600원)</t>
+          <t>소망트레이딩 6파이 400mm 옵션 5,200/개 (2026-10-20 확인) · 371 절단 요청 (안 되면 400 받아서 자름) · 소망트레이딩 배송비 3,000</t>
         </is>
       </c>
     </row>
@@ -863,14 +869,16 @@
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F10" s="33" t="n"/>
+          <t>봉(100개)</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>27000</v>
+      </c>
       <c r="G10" s="34">
         <f>D10*F10</f>
         <v/>
@@ -887,7 +895,7 @@
       </c>
       <c r="J10" s="32" t="inlineStr">
         <is>
-          <t>검색어 "평행핀 5x25" · 02 시험편(구멍 4.8/4.9/5.0)으로 압입 구멍 확정</t>
+          <t>국산 SUS 평행핀 "M5 (+)공차 / 25mm × 100개" 옵션 (공차 0~+0.01, 무료배송, 2026-10-20 확인) · 28개 필요 · 소량(30개) 해외 상품은 19,500 이나 널링 여부 불명확해 제외 · 02 시험편(구멍 4.8/4.9/5.0)으로 압입 구멍 확정</t>
         </is>
       </c>
     </row>
@@ -913,7 +921,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F11" s="33" t="n"/>
+      <c r="F11" s="33" t="n">
+        <v>440</v>
+      </c>
       <c r="G11" s="34">
         <f>D11*F11</f>
         <v/>
@@ -930,7 +940,7 @@
       </c>
       <c r="J11" s="32" t="inlineStr">
         <is>
-          <t>검색어 "평행핀 5x40"</t>
+          <t>국산 SUS 평행핀 M5 (+) 0~+0.01, 5x40 낱개 (2026-10-20 확인) · 배송비 4,000</t>
         </is>
       </c>
     </row>
@@ -953,10 +963,12 @@
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F12" s="33" t="n"/>
+          <t>개(약2m)</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>8900</v>
+      </c>
       <c r="G12" s="34">
         <f>D12*F12</f>
         <v/>
@@ -973,7 +985,7 @@
       </c>
       <c r="J12" s="32" t="inlineStr">
         <is>
-          <t>쇼어 70A 내외 · 검색어 "NBR 호스 5mm 10mm"</t>
+          <t>진공호스(카박스) 내경 5 · 외경 10 · 약 2m, 국내생산 (2026-10-20 확인) · 재질 표기 없음(고무) → 도착 후 경도 손으로 확인, 너무 무르면 실리콘 70도 5x10 으로</t>
         </is>
       </c>
     </row>
@@ -999,7 +1011,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F13" s="33" t="n"/>
+      <c r="F13" s="33" t="n">
+        <v>710</v>
+      </c>
       <c r="G13" s="34">
         <f>D13*F13</f>
         <v/>
@@ -1016,7 +1030,7 @@
       </c>
       <c r="J13" s="32" t="inlineStr">
         <is>
-          <t>검색어 "M16 큰와셔 50mm" · 두께 3 확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 스텐 대와셔 "M16 × 50mm" 옵션 = 안지름 17·바깥 50·두께 3 (상세 표 확인, 2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1056,9 @@
           <t>장</t>
         </is>
       </c>
-      <c r="F14" s="33" t="n"/>
+      <c r="F14" s="33" t="n">
+        <v>1890</v>
+      </c>
       <c r="G14" s="34">
         <f>D14*F14</f>
         <v/>
@@ -1059,7 +1075,7 @@
       </c>
       <c r="J14" s="32" t="inlineStr">
         <is>
-          <t>검색어 "코르크 시트 2mm"</t>
+          <t>콜크쉬트 연갈색 2mm × A4 × 2매 (2026-10-20 확인) · 배송비 2,500</t>
         </is>
       </c>
     </row>
@@ -1209,18 +1225,20 @@
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>안지름 6, 바깥지름 12, 폭 8, 멈춤나사형 (표준 규격)</t>
+          <t>안지름 6.1, 바깥지름 11, 폭 6, 멈춤나사형 (RC 휠 칼라, 10개)</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F18" s="33" t="n"/>
+          <t>봉(10개)</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="n">
+        <v>14800</v>
+      </c>
       <c r="G18" s="34">
         <f>D18*F18</f>
         <v/>
@@ -1237,7 +1255,7 @@
       </c>
       <c r="J18" s="32" t="inlineStr">
         <is>
-          <t>예: RS PRO 8236939 (6/12/8, 5개 묶음) · 바깥지름 12 넘으면 카트리지 구멍(13)에 안 들어감</t>
+          <t>옵션 "01 D11xd6.1xH6mm" 14,800 (해외, 무료배송, 11/4 도착 예정, 2026-10-20 확인) · 6개 필요 · 바깥 11 ≤ 12 → 카트리지 구멍(13) 통과 · 폭 6 &lt; 설계값 8 (tx.RAIL_COLLAR) 이라 간섭 검사보다 작음 · 쿠팡 6/12/8 표준품(SOH6)은 1개 10,620 이라 제외</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1281,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F19" s="33" t="n"/>
+      <c r="F19" s="33" t="n">
+        <v>50</v>
+      </c>
       <c r="G19" s="34">
         <f>D19*F19</f>
         <v/>
@@ -1280,7 +1300,7 @@
       </c>
       <c r="J19" s="32" t="inlineStr">
         <is>
-          <t>모든 볼트는 렌치볼트(머리 Ø5.5): 부품의 머리 자리가 이 크기 · 단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 스텐 유두 렌치볼트 낱개 (2026-10-20 확인) · 모든 볼트는 렌치볼트(머리 Ø5.5): 부품의 머리 자리가 이 크기</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1326,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F20" s="33" t="n"/>
+      <c r="F20" s="33" t="n">
+        <v>60</v>
+      </c>
       <c r="G20" s="34">
         <f>D20*F20</f>
         <v/>
@@ -1323,7 +1345,7 @@
       </c>
       <c r="J20" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1371,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F21" s="33" t="n"/>
+      <c r="F21" s="33" t="n">
+        <v>60</v>
+      </c>
       <c r="G21" s="34">
         <f>D21*F21</f>
         <v/>
@@ -1366,7 +1390,7 @@
       </c>
       <c r="J21" s="32" t="inlineStr">
         <is>
-          <t>모두 자가탭 · 아크릴에는 M3 와셔</t>
+          <t>모두 자가탭 · 아크릴에는 M3 와셔 · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1416,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F22" s="33" t="n"/>
+      <c r="F22" s="33" t="n">
+        <v>100</v>
+      </c>
       <c r="G22" s="34">
         <f>D22*F22</f>
         <v/>
@@ -1409,7 +1435,7 @@
       </c>
       <c r="J22" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1461,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F23" s="33" t="n"/>
+      <c r="F23" s="33" t="n">
+        <v>130</v>
+      </c>
       <c r="G23" s="34">
         <f>D23*F23</f>
         <v/>
@@ -1452,7 +1480,7 @@
       </c>
       <c r="J23" s="32" t="inlineStr">
         <is>
-          <t>냄비머리(Ø6)는 육각 자리(맞변 5.7)에 안 들어감</t>
+          <t>냄비머리(Ø6)는 육각 자리(맞변 5.7)에 안 들어감 · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 70 + 스텐 육각너트 M3 60 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1506,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F24" s="33" t="n"/>
+      <c r="F24" s="33" t="n">
+        <v>70</v>
+      </c>
       <c r="G24" s="34">
         <f>D24*F24</f>
         <v/>
@@ -1495,7 +1525,7 @@
       </c>
       <c r="J24" s="32" t="inlineStr">
         <is>
-          <t>M3×30 은 머리가 러그 위로 5mm 나와 캐리어에 닿음</t>
+          <t>M3×30 은 머리가 러그 위로 5mm 나와 캐리어에 닿음 · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1551,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F25" s="33" t="n"/>
+      <c r="F25" s="33" t="n">
+        <v>170</v>
+      </c>
       <c r="G25" s="34">
         <f>D25*F25</f>
         <v/>
@@ -1538,7 +1570,7 @@
       </c>
       <c r="J25" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1596,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F26" s="33" t="n"/>
+      <c r="F26" s="33" t="n">
+        <v>60</v>
+      </c>
       <c r="G26" s="34">
         <f>D26*F26</f>
         <v/>
@@ -1581,7 +1615,7 @@
       </c>
       <c r="J26" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>스텐 무두렌치볼트 오목끝 M3 8mm 낱개 (2026-10-20 확인) · 배송비 3,000 (리우툴 낱개 M3×8 없음)</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1630,7 @@
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>M3 (바깥지름 7)</t>
+          <t>M3 (바깥지름 8, 두께 0.5)</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
@@ -1607,7 +1641,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F27" s="33" t="n"/>
+      <c r="F27" s="33" t="n">
+        <v>20</v>
+      </c>
       <c r="G27" s="34">
         <f>D27*F27</f>
         <v/>
@@ -1624,7 +1660,7 @@
       </c>
       <c r="J27" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) "스텐 평와셔 M3x8x0.5T" (2026-10-20 확인) · 바깥 7 낱개는 쿠팡에 없어 8 로 · 속선 누름: 와셔 반지름 4 = 속선까지 거리 4 → 오히려 더 덮음, 포크 몸통 폭 18 안</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1686,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F28" s="33" t="n"/>
+      <c r="F28" s="33" t="n">
+        <v>170</v>
+      </c>
       <c r="G28" s="34">
         <f>D28*F28</f>
         <v/>
@@ -1667,7 +1705,7 @@
       </c>
       <c r="J28" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 110 + 너트 60 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1731,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F29" s="33" t="n"/>
+      <c r="F29" s="33" t="n">
+        <v>160</v>
+      </c>
       <c r="G29" s="34">
         <f>D29*F29</f>
         <v/>
@@ -1710,7 +1750,7 @@
       </c>
       <c r="J29" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 100 + 너트 60 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1776,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F30" s="33" t="n"/>
+      <c r="F30" s="33" t="n">
+        <v>190</v>
+      </c>
       <c r="G30" s="34">
         <f>D30*F30</f>
         <v/>
@@ -1753,7 +1795,7 @@
       </c>
       <c r="J30" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 130 + 너트 60 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1821,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F31" s="33" t="n"/>
+      <c r="F31" s="33" t="n">
+        <v>350</v>
+      </c>
       <c r="G31" s="34">
         <f>D31*F31</f>
         <v/>
@@ -1796,7 +1840,7 @@
       </c>
       <c r="J31" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 290 + 너트 60 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1866,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F32" s="33" t="n"/>
+      <c r="F32" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="G32" s="34">
         <f>D32*F32</f>
         <v/>
@@ -1839,7 +1885,7 @@
       </c>
       <c r="J32" s="32" t="inlineStr">
         <is>
-          <t>M5×12 이상 금지 (미끄럼 토크가 1.05N·m 까지 올라가 기어 설계 하중 초과)</t>
+          <t>M5×12 이상 금지 (미끄럼 토크가 1.05N·m 까지 올라가 기어 설계 하중 초과) · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 110 + 너트 90 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1911,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F33" s="33" t="n"/>
+      <c r="F33" s="33" t="n">
+        <v>230</v>
+      </c>
       <c r="G33" s="34">
         <f>D33*F33</f>
         <v/>
@@ -1882,7 +1930,7 @@
       </c>
       <c r="J33" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 140 + 너트 90 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1956,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F34" s="33" t="n"/>
+      <c r="F34" s="33" t="n">
+        <v>720</v>
+      </c>
       <c r="G34" s="34">
         <f>D34*F34</f>
         <v/>
@@ -1925,7 +1975,7 @@
       </c>
       <c r="J34" s="32" t="inlineStr">
         <is>
-          <t>시험 3 이 합격이면 안 씀 · 다시 주문하지 않으려고 같이 구매</t>
+          <t>시험 3 이 합격이면 안 씀 · 다시 주문하지 않으려고 같이 구매 · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 100×3 + 110×3 + 평와셔 M5x12x0.5T 30×3 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1951,7 +2001,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F35" s="33" t="n"/>
+      <c r="F35" s="33" t="n">
+        <v>550</v>
+      </c>
       <c r="G35" s="34">
         <f>D35*F35</f>
         <v/>
@@ -1968,7 +2020,7 @@
       </c>
       <c r="J35" s="32" t="inlineStr">
         <is>
-          <t>너트는 손으로 닿을 때까지만 (세게 조이면 포크가 안 돎) · 단가 미확인</t>
+          <t>너트는 손으로 닿을 때까지만 (세게 조이면 포크가 안 돎) · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 470 + 스텐 나일론너트 M5 80 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2046,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F36" s="33" t="n"/>
+      <c r="F36" s="33" t="n">
+        <v>210</v>
+      </c>
       <c r="G36" s="34">
         <f>D36*F36</f>
         <v/>
@@ -2011,7 +2065,7 @@
       </c>
       <c r="J36" s="32" t="inlineStr">
         <is>
-          <t>M6×30 이상 금지 (모터 받침: MDF 에 닿음, 페달: 가변저항 축에 닿음) · 단가 미확인</t>
+          <t>M6×30 이상 금지 (모터 받침: MDF 에 닿음, 페달: 가변저항 축에 닿음) · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2091,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F37" s="33" t="n"/>
+      <c r="F37" s="33" t="n">
+        <v>60</v>
+      </c>
       <c r="G37" s="34">
         <f>D37*F37</f>
         <v/>
@@ -2054,7 +2110,7 @@
       </c>
       <c r="J37" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 스텐 육각너트 M6 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2136,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F38" s="33" t="n"/>
+      <c r="F38" s="33" t="n">
+        <v>170</v>
+      </c>
       <c r="G38" s="34">
         <f>D38*F38</f>
         <v/>
@@ -2097,7 +2155,7 @@
       </c>
       <c r="J38" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 스텐 나일론너트 M6 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -2112,18 +2170,20 @@
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>4×16</t>
+          <t>4×16 둥근머리 1종 (스텐, 26개 봉)</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F39" s="33" t="n"/>
+          <t>봉(26개)</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="n">
+        <v>1150</v>
+      </c>
       <c r="G39" s="34">
         <f>D39*F39</f>
         <v/>
@@ -2140,7 +2200,7 @@
       </c>
       <c r="J39" s="32" t="inlineStr">
         <is>
-          <t>MDF 12T 에 10~11 박힘 · 4×20 이상은 밑으로 나옴 · 단가 미확인</t>
+          <t>옵션 "1-5 스텐둥근1종(M4) e)4x16mm-26개" (2026-10-20 확인) · 24개 필요 · 배송비 2,800 · MDF 12T 에 10~11 박힘 · 4×20 이상은 밑으로 나옴 · 머리 자리 Ø9 → 와샤머리(Ø10 내외) 안 됨</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2226,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F40" s="33" t="n"/>
+      <c r="F40" s="33" t="n">
+        <v>4440</v>
+      </c>
       <c r="G40" s="34">
         <f>D40*F40</f>
         <v/>
@@ -2183,7 +2245,7 @@
       </c>
       <c r="J40" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>Vtech 주사기 에폭시 25ml 1개 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2271,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F41" s="33" t="n"/>
+      <c r="F41" s="33" t="n">
+        <v>3000</v>
+      </c>
       <c r="G41" s="34">
         <f>D41*F41</f>
         <v/>
@@ -2226,7 +2290,7 @@
       </c>
       <c r="J41" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>탐사 젤타입 2개 (2026-10-20 확인) · 보유하면 생략</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2316,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F42" s="33" t="n"/>
+      <c r="F42" s="33" t="n">
+        <v>6900</v>
+      </c>
       <c r="G42" s="34">
         <f>D42*F42</f>
         <v/>
@@ -2269,7 +2335,7 @@
       </c>
       <c r="J42" s="32" t="inlineStr">
         <is>
-          <t>아우터가 끝판 B 구멍 Ø6·페달 받침 Ø5.6 에 들어가야 함 · 니플은 페달 팔 Ø3.4 구멍보다 커야 함</t>
+          <t>[RCM] 브레이크케이블세트 (속선 2줄 + 겉선 + 마감재, 2026-10-20 확인) · 아우터가 끝판 B 구멍 Ø6·페달 받침 Ø5.6 에 들어가야 함 (자전거 브레이크 겉선 표준 5) · 니플은 페달 팔 Ø3.4 구멍보다 커야 함</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2586,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F48" s="33" t="n"/>
+      <c r="F48" s="33" t="n">
+        <v>3993</v>
+      </c>
       <c r="G48" s="34">
         <f>D48*F48</f>
         <v/>
@@ -2537,7 +2605,7 @@
       </c>
       <c r="J48" s="32" t="inlineStr">
         <is>
-          <t>축이 톱니(널링)형이거나 20mm 면 페달에 안 맞음 · 핸들은 센서 없음 확인(2026-10-20) → 3개 · 도착 후 실측해서 페달 출력</t>
+          <t>디바이스마트(Mouser 대행) TT Electronics P160KNP-1FD15B10K 3,993(VAT 포함, 2026-10-20 확인) · 데이터시트: F형 축 Ø6 평면 4.5, L 15, 부싱 M7×0.75, 몸통 Ø16.5 · 가운데 딸깍(center detent) 있음 → 페달은 몸통 에폭시 때 딸깍 위치가 밟는 범위 밖이 되게 돌려 붙임 · 쿠팡은 전부 톱니(널링) 축이라 제외 · 반품 불가, 준비 1주 · C252 와 같이 주문 → 66,000 넘어 배송비 0</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2766,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F52" s="33" t="n"/>
+      <c r="F52" s="33" t="n">
+        <v>3100</v>
+      </c>
       <c r="G52" s="34">
         <f>D52*F52</f>
         <v/>
@@ -2715,7 +2785,7 @@
       </c>
       <c r="J52" s="32" t="inlineStr">
         <is>
-          <t>검색어 "12V 40A 릴레이 소켓" · 코일 회로에 비상정지·덮개 스위치·5V 릴레이 모듈 직렬</t>
+          <t>12v 4핀 릴레이 + 배선된 소켓 세트 40A (2026-10-20 확인) · 배송비 3,000 · 코일 회로에 비상정지·덮개 스위치·5V 릴레이 모듈 직렬</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2811,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F53" s="33" t="n"/>
+      <c r="F53" s="33" t="n">
+        <v>8900</v>
+      </c>
       <c r="G53" s="34">
         <f>D53*F53</f>
         <v/>
@@ -2758,7 +2830,7 @@
       </c>
       <c r="J53" s="32" t="inlineStr">
         <is>
-          <t>여분 퓨즈 2개 권장</t>
+          <t>12AWG 인라인 ATC/ATO 홀더 4개 + 퓨즈 12개(15A 2개 포함) (2026-10-20 확인) · 여분 퓨즈 포함</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2856,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F54" s="33" t="n"/>
+      <c r="F54" s="33" t="n">
+        <v>7700</v>
+      </c>
       <c r="G54" s="34">
         <f>D54*F54</f>
         <v/>
@@ -2801,7 +2875,7 @@
       </c>
       <c r="J54" s="32" t="inlineStr">
         <is>
-          <t>단가 미확인</t>
+          <t>(PP-B057) 22파이 1A1B KGE-H4R1R (2026-10-20 확인) · 배송비 3,000 · 22mm 판 구멍 필요</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2901,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F55" s="33" t="n"/>
+      <c r="F55" s="33" t="n">
+        <v>990</v>
+      </c>
       <c r="G55" s="34">
         <f>D55*F55</f>
         <v/>
@@ -2844,7 +2920,7 @@
       </c>
       <c r="J55" s="32" t="inlineStr">
         <is>
-          <t>로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
+          <t>아두이노 1채널 5V 릴레이 모듈 (2026-10-20 확인) · 배송비 3,000 · 로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
         </is>
       </c>
     </row>
@@ -2859,14 +2935,16 @@
       </c>
       <c r="C56" s="31" t="inlineStr"/>
       <c r="D56" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F56" s="33" t="n"/>
+          <t>봉(10개)</t>
+        </is>
+      </c>
+      <c r="F56" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="G56" s="34">
         <f>D56*F56</f>
         <v/>
@@ -2883,7 +2961,7 @@
       </c>
       <c r="J56" s="32" t="inlineStr">
         <is>
-          <t>내장 다이오드 릴레이면 생략</t>
+          <t>1N4007 10개 묶음 (2026-10-20 확인) · 배송비 2,700 · 2개 사용 (역기전력 1 + 여분) · 내장 다이오드 릴레이면 생략</t>
         </is>
       </c>
     </row>
@@ -2902,14 +2980,16 @@
         </is>
       </c>
       <c r="D57" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F57" s="33" t="n"/>
+          <t>세트(1m)</t>
+        </is>
+      </c>
+      <c r="F57" s="33" t="n">
+        <v>1310</v>
+      </c>
       <c r="G57" s="34">
         <f>D57*F57</f>
         <v/>
@@ -2926,7 +3006,7 @@
       </c>
       <c r="J57" s="32" t="inlineStr">
         <is>
-          <t>키트 배터리 선 16AWG 확인(2026-10-20) → 퓨즈 15A 유지</t>
+          <t>KDsafe 실리콘전선 16AWG 빨검 세트 1M × 2 (2026-10-20 확인) · 배송비 3,000 · 키트 배터리 선 16AWG 확인(2026-10-20) → 퓨즈 15A 유지</t>
         </is>
       </c>
     </row>
@@ -2941,18 +3021,20 @@
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>250 규격(6.3mm) 절연 암 평형 단자 + 수축 튜브</t>
+          <t>250 규격(6.3mm) 절연 암 평형 단자 (22~16AWG)</t>
         </is>
       </c>
       <c r="D58" s="31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F58" s="33" t="n"/>
+          <t>봉(2개)</t>
+        </is>
+      </c>
+      <c r="F58" s="33" t="n">
+        <v>310</v>
+      </c>
       <c r="G58" s="34">
         <f>D58*F58</f>
         <v/>
@@ -2969,7 +3051,7 @@
       </c>
       <c r="J58" s="32" t="inlineStr">
         <is>
-          <t>배터리 단자 = 6.3mm 평형 탭(사진 확인) · 홀더·소켓에 단자 포함이면 생략</t>
+          <t>6.3mm 절연 PG REC 250 빨강 2개 × 3 (2026-10-20 확인) · 배송비 3,000 · 절연형이라 수축 튜브 불필요 · 배터리 단자 = 6.3mm 평형 탭(사진 확인) · 릴레이 소켓은 배선 완성품</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3077,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F59" s="33" t="n"/>
+      <c r="F59" s="33" t="n">
+        <v>830</v>
+      </c>
       <c r="G59" s="34">
         <f>D59*F59</f>
         <v/>
@@ -3012,7 +3096,7 @@
       </c>
       <c r="J59" s="32" t="inlineStr">
         <is>
-          <t>풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
+          <t>10K 10개 330 + 4.7K 10개 500, 판매처 2곳 (배송비 3,000 × 2, 2026-10-20 확인) · 풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3122,9 @@
           <t>롤</t>
         </is>
       </c>
-      <c r="F60" s="33" t="n"/>
+      <c r="F60" s="33" t="n">
+        <v>30600</v>
+      </c>
       <c r="G60" s="34">
         <f>D60*F60</f>
         <v/>
@@ -3055,7 +3141,7 @@
       </c>
       <c r="J60" s="32" t="inlineStr">
         <is>
-          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 단가 미확인</t>
+          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 옵션 "2.85mm 화이트" 1kg 30,600 (해외, 무료배송, 11/5 도착 예정, 판매자 평가 없음, 2026-10-20 확인) · 국내 2.85 PLA 는 UltiMaker 750g 75,900 뿐</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3167,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F61" s="33" t="n"/>
+      <c r="F61" s="33" t="n">
+        <v>12250</v>
+      </c>
       <c r="G61" s="34">
         <f>D61*F61</f>
         <v/>
@@ -3098,7 +3186,7 @@
       </c>
       <c r="J61" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>에클랜드 13609 볼렌치 9pcs 1.5~10mm (2026-10-20 확인) · 보유하면 생략</t>
         </is>
       </c>
     </row>
@@ -3121,10 +3209,12 @@
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F62" s="33" t="n"/>
+          <t>갑(10개)</t>
+        </is>
+      </c>
+      <c r="F62" s="33" t="n">
+        <v>5570</v>
+      </c>
       <c r="G62" s="34">
         <f>D62*F62</f>
         <v/>
@@ -3141,7 +3231,7 @@
       </c>
       <c r="J62" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략 · 드릴이 없으면 아크릴 재단 업체에 구멍까지 주문</t>
+          <t>한도 HSS 드릴 3.4 10개 (2026-10-20 확인) · 보유하면 생략 · 드릴이 없으면 아크릴 재단 업체에 구멍까지 주문</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3253,9 @@
           <t>세트</t>
         </is>
       </c>
-      <c r="F63" s="33" t="n"/>
+      <c r="F63" s="33" t="n">
+        <v>15420</v>
+      </c>
       <c r="G63" s="34">
         <f>D63*F63</f>
         <v/>
@@ -3180,7 +3272,7 @@
       </c>
       <c r="J63" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>인두기 10종 세트 (실납 포함, 2026-10-20 확인) · 배송비 3,000 · 보유하면 생략</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3298,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F64" s="33" t="n"/>
+      <c r="F64" s="33" t="n">
+        <v>13550</v>
+      </c>
       <c r="G64" s="34">
         <f>D64*F64</f>
         <v/>
@@ -3223,7 +3317,7 @@
       </c>
       <c r="J64" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>디지털 행잉 저울 60kg / 10g 단위 (2026-10-20 확인) · 보유하면 생략</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3343,9 @@
           <t>개</t>
         </is>
       </c>
-      <c r="F65" s="33" t="n"/>
+      <c r="F65" s="33" t="n">
+        <v>7000</v>
+      </c>
       <c r="G65" s="34">
         <f>D65*F65</f>
         <v/>
@@ -3266,7 +3362,7 @@
       </c>
       <c r="J65" s="32" t="inlineStr">
         <is>
-          <t>보유하면 생략</t>
+          <t>종원 디지털 캘리퍼스 201-150 (2026-10-20 확인) · 보유하면 생략</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3388,9 @@
           <t>식</t>
         </is>
       </c>
-      <c r="F66" s="33" t="n"/>
+      <c r="F66" s="33" t="n">
+        <v>70900</v>
+      </c>
       <c r="G66" s="34">
         <f>D66*F66</f>
         <v/>
@@ -3305,7 +3403,7 @@
       </c>
       <c r="J66" s="32" t="inlineStr">
         <is>
-          <t>v3 는 22,900원 · 새 항목 판매처에 따라 달라짐 (미확인)</t>
+          <t>v3 22,900 + 새 판매처 48,000 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 비상정지 3,000 · 5V 모듈 3,000 · 1N4007 2,700 · 전선 3,000 · 압착단자 3,000 · 저항 3,000×2 · 납땜 3,000 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송 · 보유 공구 생략하면 줄어듦</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3547,12 @@
       </c>
       <c r="B2" s="42" t="inlineStr">
         <is>
-          <t>압축 스프링 C252 9개, C147 3개</t>
+          <t>압축 스프링 C252 9개, C147 3개, 가변저항 P160KNP-1FD15B10K 3개</t>
         </is>
       </c>
       <c r="C2" s="42" t="inlineStr">
         <is>
-          <t>한 장바구니로 주문. C252 = 1개 8,360원(VAT 포함), 수량 9 로 내려감 확인(2026-10-20), 반품·취소 불가, 준비 4~5일. C252: https://www.devicemart.co.kr/goods/view?no=15336269 / C147: https://www.devicemart.co.kr/goods/view?no=15336164 (외경 5, 자유장 10, P1 1.77N@6.47, P2 2.79N@4.41 인지 확인)</t>
+          <t>한 장바구니로 주문 (합계 66,000 이상 → 배송비 0). C252 = 1개 8,360원(VAT 포함), 수량 9 로 내려감 확인(2026-10-20), 반품·취소 불가, 준비 4~5일. C252: https://www.devicemart.co.kr/goods/view?no=15336269 / C147: https://www.devicemart.co.kr/goods/view?no=15336164 (외경 5, 자유장 10, P1 1.77N@6.47, P2 2.79N@4.41 인지 확인) / 가변저항: https://www.devicemart.co.kr/goods/view?no=16130996 (Mouser 대행, TT Electronics P160 F형 D축 Ø6·평면 4.5·L15·부싱 M7×0.75, 가운데 딸깍 있음, 반품 불가, 준비 1주. 쿠팡 B10K 는 전부 톱니 축이라 여기서)</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3586,7 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>구매목록 시트의 품명을 누르면 쿠팡 상품·검색. 고를 때 규격 칸과 맞춰 볼 것: ① 가변저항 = 축 Ø6 반달(D컷) 15mm + 부싱 M7 (톱니 축·20mm 안 됨) ② 볼트 = 렌치볼트(육각 홈, 머리 Ø5.5) — 냄비머리 안 됨 ③ 샤프트 칼라 = 안지름 6, 바깥지름 12 이하 ④ 6003ZZ = 17×35×10 ⑤ 평행핀 = Ø5 정확히 (25·40 길이) ⑥ PLA = 2.85mm ⑦ 목재나사 = 4×16 (4×20 이상 안 됨)</t>
+          <t>구매목록 시트의 품명을 누르면 고른 쿠팡 상품 (2026-10-20 확인). 옵션이 있는 상품은 비고 칸의 옵션 이름으로 고를 것. 볼트·너트·와셔(M3 무두볼트 빼고)는 리우툴(판매자 우진카본볼트) 한 판매자 → 한 장바구니. 고른 상품은 아래 7가지를 지킴: ① 가변저항 = 축 Ø6 반달(D컷) 15mm + 부싱 M7 (톱니 축·20mm 안 됨) ② 볼트 = 렌치볼트(육각 홈, 머리 Ø5.5) — 냄비머리 안 됨 ③ 샤프트 칼라 = 안지름 6, 바깥지름 12 이하 ④ 6003ZZ = 17×35×10 ⑤ 평행핀 = Ø5 정확히 (25·40 길이) ⑥ PLA = 2.85mm ⑦ 목재나사 = 4×16 (4×20 이상 안 됨)</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>육각 렌치 세트</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>2.5·3·4·5mm 포함</t>
+          <t>새 판매처 포함</t>
         </is>
       </c>
       <c r="D61" s="31" t="n">
@@ -3164,21 +3164,17 @@
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>식</t>
         </is>
       </c>
       <c r="F61" s="33" t="n">
-        <v>12250</v>
+        <v>67900</v>
       </c>
       <c r="G61" s="34">
         <f>D61*F61</f>
         <v/>
       </c>
-      <c r="H61" s="32" t="inlineStr">
-        <is>
-          <t>렌치볼트 M3~M6, 무두볼트</t>
-        </is>
-      </c>
+      <c r="H61" s="32" t="n"/>
       <c r="I61" s="32" t="inlineStr">
         <is>
           <t>확정</t>
@@ -3186,257 +3182,40 @@
       </c>
       <c r="J61" s="32" t="inlineStr">
         <is>
-          <t>에클랜드 13609 볼렌치 9pcs 1.5~10mm (2026-10-20 확인) · 보유하면 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="29.25" customHeight="1" s="16">
-      <c r="A62" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="32" t="inlineStr">
-        <is>
-          <t>드릴 날</t>
-        </is>
-      </c>
-      <c r="C62" s="31" t="inlineStr">
-        <is>
-          <t>Ø3.4 (전동 드릴용)</t>
-        </is>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="32" t="inlineStr">
-        <is>
-          <t>갑(10개)</t>
-        </is>
-      </c>
-      <c r="F62" s="33" t="n">
-        <v>5570</v>
-      </c>
-      <c r="G62" s="34">
-        <f>D62*F62</f>
-        <v/>
-      </c>
-      <c r="H62" s="32" t="inlineStr">
-        <is>
-          <t>아크릴 나사 구멍 14 (설계서 5장 위치)</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J62" s="32" t="inlineStr">
-        <is>
-          <t>한도 HSS 드릴 3.4 10개 (2026-10-20 확인) · 보유하면 생략 · 드릴이 없으면 아크릴 재단 업체에 구멍까지 주문</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="29.25" customHeight="1" s="16">
-      <c r="A63" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="32" t="inlineStr">
-        <is>
-          <t>납땜 인두 + 실납</t>
-        </is>
-      </c>
-      <c r="C63" s="31" t="inlineStr"/>
-      <c r="D63" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="32" t="inlineStr">
-        <is>
-          <t>세트</t>
-        </is>
-      </c>
-      <c r="F63" s="33" t="n">
-        <v>15420</v>
-      </c>
-      <c r="G63" s="34">
-        <f>D63*F63</f>
-        <v/>
-      </c>
-      <c r="H63" s="32" t="inlineStr">
-        <is>
-          <t>만능기판 (분압 저항·다이오드·배선)</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J63" s="32" t="inlineStr">
-        <is>
-          <t>인두기 10종 세트 (실납 포함, 2026-10-20 확인) · 배송비 3,000 · 보유하면 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="29.25" customHeight="1" s="16">
-      <c r="A64" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="32" t="inlineStr">
-        <is>
-          <t>걸이 저울</t>
-        </is>
-      </c>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>0~5kg, 10g 단위</t>
-        </is>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="32" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F64" s="33" t="n">
-        <v>13550</v>
-      </c>
-      <c r="G64" s="34">
-        <f>D64*F64</f>
-        <v/>
-      </c>
-      <c r="H64" s="32" t="inlineStr">
-        <is>
-          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J64" s="32" t="inlineStr">
-        <is>
-          <t>디지털 행잉 저울 60kg / 10g 단위 (2026-10-20 확인) · 보유하면 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="29.25" customHeight="1" s="16">
-      <c r="A65" s="31" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="32" t="inlineStr">
-        <is>
-          <t>디지털 캘리퍼스</t>
-        </is>
-      </c>
-      <c r="C65" s="31" t="inlineStr">
-        <is>
-          <t>0.01mm 표시, 150mm</t>
-        </is>
-      </c>
-      <c r="D65" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="32" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F65" s="33" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G65" s="34">
-        <f>D65*F65</f>
-        <v/>
-      </c>
-      <c r="H65" s="32" t="inlineStr">
-        <is>
-          <t>쿠폰·핀 구멍·축 지름 확인</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J65" s="32" t="inlineStr">
-        <is>
-          <t>종원 디지털 캘리퍼스 201-150 (2026-10-20 확인) · 보유하면 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="29.25" customHeight="1" s="16">
-      <c r="A66" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="32" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C66" s="31" t="inlineStr">
-        <is>
-          <t>새 판매처 포함</t>
-        </is>
-      </c>
-      <c r="D66" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="32" t="inlineStr">
-        <is>
-          <t>식</t>
-        </is>
-      </c>
-      <c r="F66" s="33" t="n">
-        <v>70900</v>
-      </c>
-      <c r="G66" s="34">
-        <f>D66*F66</f>
-        <v/>
-      </c>
-      <c r="H66" s="32" t="n"/>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J66" s="32" t="inlineStr">
-        <is>
-          <t>v3 22,900 + 새 판매처 48,000 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 비상정지 3,000 · 5V 모듈 3,000 · 1N4007 2,700 · 전선 3,000 · 압착단자 3,000 · 저항 3,000×2 · 납땜 3,000 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송 · 보유 공구 생략하면 줄어듦</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="38" t="inlineStr">
+          <t>v3 22,900 + 새 판매처 45,000 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 비상정지 3,000 · 5V 모듈 3,000 · 1N4007 2,700 · 전선 3,000 · 압착단자 3,000 · 저항 3,000×2 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>합계 (확정 항목, 단가 입력된 것만)</t>
         </is>
       </c>
-      <c r="G67" s="39">
-        <f>SUMIFS(G5:G66,I5:I66,"확정")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="38" t="inlineStr">
+      <c r="G62" s="39">
+        <f>SUMIFS(G5:G61,I5:I61,"확정")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="38" t="inlineStr">
         <is>
           <t>합계 (선택 포함)</t>
         </is>
       </c>
-      <c r="G68" s="39">
-        <f>SUM(G5:G66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="38" t="inlineStr">
+      <c r="G63" s="39">
+        <f>SUM(G5:G61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="38" t="inlineStr">
         <is>
           <t>단가 미확인 항목 수</t>
         </is>
       </c>
-      <c r="G69" s="40">
-        <f>COUNTBLANK(F5:F66)</f>
+      <c r="G64" s="40">
+        <f>COUNTBLANK(F5:F61)</f>
         <v/>
       </c>
     </row>
@@ -3498,11 +3277,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3514,7 +3288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="1"/>
@@ -3593,15 +3367,32 @@
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
         <is>
+          <t>공구 (보유, 목록에서 뺌)</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납, 걸이 저울 0~5kg(10g), 디지털 캘리퍼스(0.01mm)</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>렌치볼트·무두볼트 / 아크릴 나사 구멍 14 (드릴이 없으면 아크릴 재단 업체에 구멍까지 주문) / 만능기판 / 클러치 미끄럼·끌림 토크 시험 / 쿠폰·핀 구멍·축 지름·가변저항 실측</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
           <t>도착 후</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>① 가변저항 축 지름·평면·길이 실측 → 80·82 페달 출력 (다르면 수정) ② 핀·6003 도착 → 02 시험편 출력 ③ 00 쿠폰 구멍마다 안 들어감/꽉/헐거움 → 공차 확정 후 전체 출력 ④ C252 안지름 실측 (12.5 이상)</t>
         </is>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>배송비</t>
+          <t>걸이 저울</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>새 판매처 포함</t>
+          <t>0~5kg, 10g 단위</t>
         </is>
       </c>
       <c r="D61" s="31" t="n">
@@ -3164,17 +3164,21 @@
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>식</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F61" s="33" t="n">
-        <v>67900</v>
+        <v>13550</v>
       </c>
       <c r="G61" s="34">
         <f>D61*F61</f>
         <v/>
       </c>
-      <c r="H61" s="32" t="n"/>
+      <c r="H61" s="32" t="inlineStr">
+        <is>
+          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
+        </is>
+      </c>
       <c r="I61" s="32" t="inlineStr">
         <is>
           <t>확정</t>
@@ -3182,40 +3186,126 @@
       </c>
       <c r="J61" s="32" t="inlineStr">
         <is>
+          <t>디지털 행잉 저울 60kg / 10g 단위 (2026-10-20 확인) · 무료배송</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="29.25" customHeight="1" s="16">
+      <c r="A62" s="31" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>디지털 캘리퍼스</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>0.01mm 표시, 150mm</t>
+        </is>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F62" s="33" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G62" s="34">
+        <f>D62*F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>쿠폰·핀 구멍·축 지름·가변저항 실측</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>종원 디지털 캘리퍼스 201-150 (2026-10-20 확인) · 무료배송</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="29.25" customHeight="1" s="16">
+      <c r="A63" s="31" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>배송비</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>새 판매처 포함</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="32" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="F63" s="33" t="n">
+        <v>67900</v>
+      </c>
+      <c r="G63" s="34">
+        <f>D63*F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="32" t="n"/>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J63" s="32" t="inlineStr">
+        <is>
           <t>v3 22,900 + 새 판매처 45,000 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 비상정지 3,000 · 5V 모듈 3,000 · 1N4007 2,700 · 전선 3,000 · 압착단자 3,000 · 저항 3,000×2 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송</t>
         </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="38" t="inlineStr">
-        <is>
-          <t>합계 (확정 항목, 단가 입력된 것만)</t>
-        </is>
-      </c>
-      <c r="G62" s="39">
-        <f>SUMIFS(G5:G61,I5:I61,"확정")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="38" t="inlineStr">
-        <is>
-          <t>합계 (선택 포함)</t>
-        </is>
-      </c>
-      <c r="G63" s="39">
-        <f>SUM(G5:G61)</f>
-        <v/>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="38" t="inlineStr">
         <is>
+          <t>합계 (확정 항목, 단가 입력된 것만)</t>
+        </is>
+      </c>
+      <c r="G64" s="39">
+        <f>SUMIFS(G5:G63,I5:I63,"확정")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="38" t="inlineStr">
+        <is>
+          <t>합계 (선택 포함)</t>
+        </is>
+      </c>
+      <c r="G65" s="39">
+        <f>SUM(G5:G63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="38" t="inlineStr">
+        <is>
           <t>단가 미확인 항목 수</t>
         </is>
       </c>
-      <c r="G64" s="40">
-        <f>COUNTBLANK(F5:F61)</f>
+      <c r="G66" s="40">
+        <f>COUNTBLANK(F5:F63)</f>
         <v/>
       </c>
     </row>
@@ -3277,6 +3367,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3372,12 +3464,12 @@
       </c>
       <c r="B5" s="42" t="inlineStr">
         <is>
-          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납, 걸이 저울 0~5kg(10g), 디지털 캘리퍼스(0.01mm)</t>
+          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납</t>
         </is>
       </c>
       <c r="C5" s="42" t="inlineStr">
         <is>
-          <t>렌치볼트·무두볼트 / 아크릴 나사 구멍 14 (드릴이 없으면 아크릴 재단 업체에 구멍까지 주문) / 만능기판 / 클러치 미끄럼·끌림 토크 시험 / 쿠폰·핀 구멍·축 지름·가변저항 실측</t>
+          <t>렌치볼트·무두볼트 / 아크릴 나사 구멍 14 (드릴이 없으면 아크릴 재단 업체에 구멍까지 주문) / 만능기판</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -2530,19 +2530,19 @@
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>Ø6×3mm 40개</t>
+          <t>Ø6×3mm</t>
         </is>
       </c>
       <c r="D47" s="31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F47" s="33" t="n">
-        <v>11300</v>
+        <v>220</v>
       </c>
       <c r="G47" s="34">
         <f>D47*F47</f>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H47" s="32" t="inlineStr">
         <is>
-          <t>러그 3 + 표시 바퀴 4</t>
+          <t>러그 3 + 표시 바퀴 4 (+여분 3)</t>
         </is>
       </c>
       <c r="I47" s="32" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="J47" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /7119515778</t>
+          <t>디바이스마트 ND 원형자석 6Ø x 3t, 최소 10개 (2026-10-20 확인) · 쿠팡 40개 봉(11,300) 대신</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>20개 묶음</t>
+          <t>하프 사이즈 89×52 (브레드보드형, 양면)</t>
         </is>
       </c>
       <c r="D51" s="31" t="n">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F51" s="33" t="n">
-        <v>15000</v>
+        <v>2420</v>
       </c>
       <c r="G51" s="34">
         <f>D51*F51</f>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="J51" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /9661304796</t>
+          <t>디바이스마트 일렉트로쿠키 브레드보드형 만능기판 Half (2026-10-20 확인) · 쿠팡 20장 묶음(15,000) 대신</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F54" s="33" t="n">
-        <v>7700</v>
+        <v>7370</v>
       </c>
       <c r="G54" s="34">
         <f>D54*F54</f>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="J54" s="32" t="inlineStr">
         <is>
-          <t>(PP-B057) 22파이 1A1B KGE-H4R1R (2026-10-20 확인) · 배송비 3,000 · 22mm 판 구멍 필요</t>
+          <t>디바이스마트 KGAUTO KGE-C4R1R 25Φ 푸쉬록턴 리셋 1a1b (2026-10-20 확인) · 준비 2주 · 25mm 판 구멍 필요</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>1채널</t>
+          <t>1채널, 로우 트리거</t>
         </is>
       </c>
       <c r="D55" s="31" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="J55" s="32" t="inlineStr">
         <is>
-          <t>아두이노 1채널 5V 릴레이 모듈 (2026-10-20 확인) · 배송비 3,000 · 로우 트리거 기준. 하이 트리거면 펌웨어 RELAY_ACTIVE_LOW=false</t>
+          <t>디바이스마트 SZH-RLBG-007 Low-Trigger (2026-10-20 확인) · 펌웨어 RELAY_ACTIVE_LOW 기본값(로우)과 맞음</t>
         </is>
       </c>
     </row>
@@ -2935,15 +2935,15 @@
       </c>
       <c r="C56" s="31" t="inlineStr"/>
       <c r="D56" s="31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>봉(10개)</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F56" s="33" t="n">
-        <v>200</v>
+        <v>22</v>
       </c>
       <c r="G56" s="34">
         <f>D56*F56</f>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>주 릴레이 코일 역기전력 흡수 1 + 여분 1</t>
+          <t>주 릴레이 코일 역기전력 흡수 1 + 여분</t>
         </is>
       </c>
       <c r="I56" s="32" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="J56" s="32" t="inlineStr">
         <is>
-          <t>1N4007 10개 묶음 (2026-10-20 확인) · 배송비 2,700 · 2개 사용 (역기전력 1 + 여분) · 내장 다이오드 릴레이면 생략</t>
+          <t>디바이스마트 1N4007, 최소 10개 (2026-10-20 확인) · 내장 다이오드 릴레이면 생략</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>10kΩ 1개 + 4.7kΩ 1개 (1/4W)</t>
+          <t>10kΩ 30개 + 4.7kΩ 30개 (1/4W, 최소 수량)</t>
         </is>
       </c>
       <c r="D59" s="31" t="n">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="F59" s="33" t="n">
-        <v>830</v>
+        <v>1518</v>
       </c>
       <c r="G59" s="34">
         <f>D59*F59</f>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="J59" s="32" t="inlineStr">
         <is>
-          <t>10K 10개 330 + 4.7K 10개 500, 판매처 2곳 (배송비 3,000 × 2, 2026-10-20 확인) · 풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
+          <t>디바이스마트 제일전자 103J·472J 각 30개 × 25.3원 (2026-10-20 확인) · 1개씩 사용 · 풀었을 때 페달을 떼야 재시동 (펌웨어)</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="F63" s="33" t="n">
-        <v>67900</v>
+        <v>53200</v>
       </c>
       <c r="G63" s="34">
         <f>D63*F63</f>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="J63" s="32" t="inlineStr">
         <is>
-          <t>v3 22,900 + 새 판매처 45,000 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 비상정지 3,000 · 5V 모듈 3,000 · 1N4007 2,700 · 전선 3,000 · 압착단자 3,000 · 저항 3,000×2 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송</t>
+          <t>v3 22,900 + 새 판매처 30,300 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 전선 3,000 · 압착단자 3,000 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="B2" s="42" t="inlineStr">
         <is>
-          <t>압축 스프링 C252 9개, C147 3개, 가변저항 P160KNP-1FD15B10K 3개</t>
+          <t>압축 스프링 C252 9개, C147 3개, 가변저항 P160KNP-1FD15B10K 3개, 5V 릴레이 모듈, 1N4007, 저항, 비상정지 스위치, 만능기판, 자석 10개</t>
         </is>
       </c>
       <c r="C2" s="42" t="inlineStr">

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>걸이 저울</t>
+          <t>디지털 캘리퍼스</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>0~5kg, 10g 단위</t>
+          <t>0.01mm 표시, 150mm</t>
         </is>
       </c>
       <c r="D61" s="31" t="n">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="F61" s="33" t="n">
-        <v>13550</v>
+        <v>7000</v>
       </c>
       <c r="G61" s="34">
         <f>D61*F61</f>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H61" s="32" t="inlineStr">
         <is>
-          <t>클러치 미끄럼 토크·끌림 토크 측정</t>
+          <t>쿠폰·핀 구멍·축 지름·가변저항 실측</t>
         </is>
       </c>
       <c r="I61" s="32" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J61" s="32" t="inlineStr">
         <is>
-          <t>디지털 행잉 저울 60kg / 10g 단위 (2026-10-20 확인) · 무료배송</t>
+          <t>종원 디지털 캘리퍼스 201-150 (2026-10-20 확인) · 무료배송</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>0.01mm 표시, 150mm</t>
+          <t>새 판매처 포함</t>
         </is>
       </c>
       <c r="D62" s="31" t="n">
@@ -3209,21 +3209,17 @@
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>식</t>
         </is>
       </c>
       <c r="F62" s="33" t="n">
-        <v>7000</v>
+        <v>53200</v>
       </c>
       <c r="G62" s="34">
         <f>D62*F62</f>
         <v/>
       </c>
-      <c r="H62" s="32" t="inlineStr">
-        <is>
-          <t>쿠폰·핀 구멍·축 지름·가변저항 실측</t>
-        </is>
-      </c>
+      <c r="H62" s="32" t="n"/>
       <c r="I62" s="32" t="inlineStr">
         <is>
           <t>확정</t>
@@ -3231,81 +3227,40 @@
       </c>
       <c r="J62" s="32" t="inlineStr">
         <is>
-          <t>종원 디지털 캘리퍼스 201-150 (2026-10-20 확인) · 무료배송</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="29.25" customHeight="1" s="16">
-      <c r="A63" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="32" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C63" s="31" t="inlineStr">
-        <is>
-          <t>새 판매처 포함</t>
-        </is>
-      </c>
-      <c r="D63" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="32" t="inlineStr">
-        <is>
-          <t>식</t>
-        </is>
-      </c>
-      <c r="F63" s="33" t="n">
-        <v>53200</v>
-      </c>
-      <c r="G63" s="34">
-        <f>D63*F63</f>
-        <v/>
-      </c>
-      <c r="H63" s="32" t="n"/>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J63" s="32" t="inlineStr">
-        <is>
           <t>v3 22,900 + 새 판매처 30,300 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 전선 3,000 · 압착단자 3,000 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송</t>
         </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="38" t="inlineStr">
+        <is>
+          <t>합계 (확정 항목, 단가 입력된 것만)</t>
+        </is>
+      </c>
+      <c r="G63" s="39">
+        <f>SUMIFS(G5:G62,I5:I62,"확정")</f>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="38" t="inlineStr">
         <is>
-          <t>합계 (확정 항목, 단가 입력된 것만)</t>
+          <t>합계 (선택 포함)</t>
         </is>
       </c>
       <c r="G64" s="39">
-        <f>SUMIFS(G5:G63,I5:I63,"확정")</f>
+        <f>SUM(G5:G62)</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="38" t="inlineStr">
         <is>
-          <t>합계 (선택 포함)</t>
-        </is>
-      </c>
-      <c r="G65" s="39">
-        <f>SUM(G5:G63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="38" t="inlineStr">
-        <is>
           <t>단가 미확인 항목 수</t>
         </is>
       </c>
-      <c r="G66" s="40">
-        <f>COUNTBLANK(F5:F63)</f>
+      <c r="G65" s="40">
+        <f>COUNTBLANK(F5:F62)</f>
         <v/>
       </c>
     </row>
@@ -3368,7 +3323,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3464,7 +3418,7 @@
       </c>
       <c r="B5" s="42" t="inlineStr">
         <is>
-          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납</t>
+          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납, 걸이 저울 0~5kg(10g 단위, 시험 3 클러치 토크용: 빌려서)</t>
         </is>
       </c>
       <c r="C5" s="42" t="inlineStr">

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="16" min="1" max="1"/>
@@ -3106,34 +3106,30 @@
       </c>
       <c r="B60" s="32" t="inlineStr">
         <is>
-          <t>PLA 필라멘트</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>2.85mm, 1kg 롤</t>
+          <t>새 판매처 포함</t>
         </is>
       </c>
       <c r="D60" s="31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" s="32" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>식</t>
         </is>
       </c>
       <c r="F60" s="33" t="n">
-        <v>30600</v>
+        <v>53200</v>
       </c>
       <c r="G60" s="34">
         <f>D60*F60</f>
         <v/>
       </c>
-      <c r="H60" s="32" t="inlineStr">
-        <is>
-          <t>출력 예상 4.05kg + 실패 여유 15% − 보유 750g 롤 1개</t>
-        </is>
-      </c>
+      <c r="H60" s="32" t="n"/>
       <c r="I60" s="32" t="inlineStr">
         <is>
           <t>확정</t>
@@ -3141,126 +3137,40 @@
       </c>
       <c r="J60" s="32" t="inlineStr">
         <is>
-          <t>PrusaSlicer 추정 (Cura 와 다를 수 있음) · 옵션 "2.85mm 화이트" 1kg 30,600 (해외, 무료배송, 11/5 도착 예정, 판매자 평가 없음, 2026-10-20 확인) · 국내 2.85 PLA 는 UltiMaker 750g 75,900 뿐</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="29.25" customHeight="1" s="16">
-      <c r="A61" s="31" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="32" t="inlineStr">
-        <is>
-          <t>디지털 캘리퍼스</t>
-        </is>
-      </c>
-      <c r="C61" s="31" t="inlineStr">
-        <is>
-          <t>0.01mm 표시, 150mm</t>
-        </is>
-      </c>
-      <c r="D61" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="32" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F61" s="33" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G61" s="34">
-        <f>D61*F61</f>
-        <v/>
-      </c>
-      <c r="H61" s="32" t="inlineStr">
-        <is>
-          <t>쿠폰·핀 구멍·축 지름·가변저항 실측</t>
-        </is>
-      </c>
-      <c r="I61" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J61" s="32" t="inlineStr">
-        <is>
-          <t>종원 디지털 캘리퍼스 201-150 (2026-10-20 확인) · 무료배송</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="29.25" customHeight="1" s="16">
-      <c r="A62" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="32" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C62" s="31" t="inlineStr">
-        <is>
-          <t>새 판매처 포함</t>
-        </is>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="32" t="inlineStr">
-        <is>
-          <t>식</t>
-        </is>
-      </c>
-      <c r="F62" s="33" t="n">
-        <v>53200</v>
-      </c>
-      <c r="G62" s="34">
-        <f>D62*F62</f>
-        <v/>
-      </c>
-      <c r="H62" s="32" t="n"/>
-      <c r="I62" s="32" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="J62" s="32" t="inlineStr">
-        <is>
           <t>v3 22,900 + 새 판매처 30,300 (2026-10-20 확인): KYK 3,000 · 평행핀 5x40 4,000 · 리우툴 3,000 · 무두볼트 3,000 · 목재나사 2,800 · 코르크 2,500 · 릴레이 3,000 · 전선 3,000 · 압착단자 3,000 · 소망트레이딩 3,000 / 디바이스마트(66,000 이상)·나머지 무료배송</t>
         </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="38" t="inlineStr">
+        <is>
+          <t>합계 (확정 항목, 단가 입력된 것만)</t>
+        </is>
+      </c>
+      <c r="G61" s="39">
+        <f>SUMIFS(G5:G60,I5:I60,"확정")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="38" t="inlineStr">
+        <is>
+          <t>합계 (선택 포함)</t>
+        </is>
+      </c>
+      <c r="G62" s="39">
+        <f>SUM(G5:G60)</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="38" t="inlineStr">
         <is>
-          <t>합계 (확정 항목, 단가 입력된 것만)</t>
-        </is>
-      </c>
-      <c r="G63" s="39">
-        <f>SUMIFS(G5:G62,I5:I62,"확정")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="38" t="inlineStr">
-        <is>
-          <t>합계 (선택 포함)</t>
-        </is>
-      </c>
-      <c r="G64" s="39">
-        <f>SUM(G5:G62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="38" t="inlineStr">
-        <is>
           <t>단가 미확인 항목 수</t>
         </is>
       </c>
-      <c r="G65" s="40">
-        <f>COUNTBLANK(F5:F62)</f>
+      <c r="G63" s="40">
+        <f>COUNTBLANK(F5:F60)</f>
         <v/>
       </c>
     </row>
@@ -3321,8 +3231,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3334,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="1"/>
@@ -3418,7 +3326,7 @@
       </c>
       <c r="B5" s="42" t="inlineStr">
         <is>
-          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납, 걸이 저울 0~5kg(10g 단위, 시험 3 클러치 토크용: 빌려서)</t>
+          <t>육각 렌치 2.5·3·4·5, 드릴 + Ø3.4 날, 납땜 인두·실납, 걸이 저울 0~5kg(10g 단위, 시험 3 클러치 토크용), 디지털 캘리퍼스(0.01mm, 학교 것)</t>
         </is>
       </c>
       <c r="C5" s="42" t="inlineStr">
@@ -3430,15 +3338,32 @@
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
         <is>
+          <t>PLA (따로 준비)</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>2.85mm PLA 약 4.7kg (보유 750g 빼면 1kg 롤 4개)</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>구매 신청에서 뺌. 출력 예상 4.05kg + 실패 여유 15% (PrusaSlicer 추정). Ultimaker 2+ 용 2.85mm. 쿠팡 해외 1kg 30,600원(11/5 도착) 또는 국내 UltiMaker 750g 75,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
           <t>도착 후</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>① 가변저항 축 지름·평면·길이 실측 → 80·82 페달 출력 (다르면 수정) ② 핀·6003 도착 → 02 시험편 출력 ③ 00 쿠폰 구멍마다 안 들어감/꽉/헐거움 → 공차 확정 후 전체 출력 ④ C252 안지름 실측 (12.5 이상)</t>
         </is>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>게시판·카카오톡에 아래 문구 그대로: "열처리 연마봉 Ø12 를 아래처럼 절단·가공 가능한지, 가격이 얼마인지 문의드립니다. 1) 435mm 1개, 2) 358mm 1개: 두 개 모두 전체 길이 양면 D컷 (마주 보는 두 면, 면 사이 10.0mm, 한쪽 깊이 1.0mm) 3) 160mm 1개, 4) 55mm 1개: 가공 없음 5) Ø6 연마봉 371mm 3개: 가공 없음. 길이 오차 ±0.5mm 이내 가능한지도 알려 주세요." → D컷 불가면 435·358 만 미스미 양면 D컷 샤프트(길이 지정)로, 나머지는 소망트레이딩</t>
+          <t>D컷 가공을 맡김. 게시판·카카오톡에 도면(v4/도면_D컷축.svg)을 첨부하고 아래 문구 그대로 견적 요청: "열처리 연마봉 Ø12 를 아래처럼 절단·가공해 주시고 가격을 알려 주세요. 1) 435mm 1개, 2) 358mm 1개: 두 개 모두 전체 길이 양면 D컷 (마주 보는 두 면, 면 사이 10.0mm, 한쪽 깊이 1.0mm) 3) 160mm 1개, 4) 55mm 1개: 가공 없음 5) Ø6 연마봉 371mm 3개: 가공 없음. 길이 오차 ±0.5mm 이내 가능한지도 알려 주세요." 열처리봉이 가공 어렵다고 하면 S45C 비열처리 연마봉으로 해도 됨 (축 안전율 14 이상이라 강도 문제 없음). 견적이 오면 구매신청 "축 양면 D컷 가공" 줄에 금액을 넣음</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>D컷 가공을 맡김. 게시판·카카오톡에 도면(v4/도면_D컷축.svg)을 첨부하고 아래 문구 그대로 견적 요청: "열처리 연마봉 Ø12 를 아래처럼 절단·가공해 주시고 가격을 알려 주세요. 1) 435mm 1개, 2) 358mm 1개: 두 개 모두 전체 길이 양면 D컷 (마주 보는 두 면, 면 사이 10.0mm, 한쪽 깊이 1.0mm) 3) 160mm 1개, 4) 55mm 1개: 가공 없음 5) Ø6 연마봉 371mm 3개: 가공 없음. 길이 오차 ±0.5mm 이내 가능한지도 알려 주세요." 열처리봉이 가공 어렵다고 하면 S45C 비열처리 연마봉으로 해도 됨 (축 안전율 14 이상이라 강도 문제 없음). 견적이 오면 구매신청 "축 양면 D컷 가공" 줄에 금액을 넣음</t>
+          <t>D컷 가공을 맡김. 게시판·카카오톡에 도면(v4/도면_D컷축.pdf 또는 .png)을 첨부하고 아래 문구 그대로 견적 요청: "열처리 연마봉 Ø12 를 아래처럼 절단·가공해 주시고 가격을 알려 주세요. 1) 435mm 1개, 2) 358mm 1개: 두 개 모두 전체 길이 양면 D컷 (마주 보는 두 면, 면 사이 10.0mm, 한쪽 깊이 1.0mm) 3) 160mm 1개, 4) 55mm 1개: 가공 없음 5) Ø6 연마봉 371mm 3개: 가공 없음. 길이 오차 ±0.5mm 이내 가능한지도 알려 주세요." 열처리봉이 가공 어렵다고 하면 S45C 비열처리 연마봉으로 해도 됨 (축 안전율 14 이상이라 강도 문제 없음). 견적이 오면 구매신청 "축 양면 D컷 가공" 줄에 금액을 넣음</t>
         </is>
       </c>
     </row>

--- a/v4/구매목록_v4.xlsx
+++ b/v4/구매목록_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="구매목록_v4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="주문방법" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="구매목록_v3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="구매목록_v2(9-25)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주문방법" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구매목록_v2(9-25)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J23" s="32" t="inlineStr">
         <is>
-          <t>냄비머리(Ø6)는 육각 자리(맞변 5.7)에 안 들어감 · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 70 + 스텐 육각너트 M3 60 (2026-10-20 확인)</t>
+          <t>유두(둥근머리) Ø5.7 → 슬리브 육각 자리를 맞변 6.2 로 넓힘 (2026-10-22) · 냄비머리(Ø6)는 안 됨 · 리우툴(판매자 우진카본볼트, 한 번 배송비 3,000) 볼트 70 + 스텐 육각너트 M3 60 (2026-10-20 확인)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="D46" s="31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H46" s="32" t="inlineStr">
         <is>
-          <t>기어 위치 6 + 출력 rpm 1</t>
+          <t>기어 위치 6 + 출력 rpm 1 + 여분 3</t>
         </is>
       </c>
       <c r="I46" s="32" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="J46" s="32" t="inlineStr">
         <is>
-          <t>v3 단가 · 쿠팡 /8520223332</t>
+          <t>v3 단가 · 쿠팡 /8520223332 · 다리가 부러지면 다시 주문해야 해서 여분 3 (같은 배송)</t>
         </is>
       </c>
     </row>
